--- a/AAII_Financials/Quarterly/FPAFY_QTR_FIN.xlsx
+++ b/AAII_Financials/Quarterly/FPAFY_QTR_FIN.xlsx
@@ -22,7 +22,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="387" uniqueCount="92">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="427" uniqueCount="92">
   <si>
     <t>FPAFY</t>
   </si>
@@ -656,23 +656,23 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <sheetPr codeName="Sheet2"/>
-  <dimension ref="A5:AE102"/>
+  <dimension ref="A5:AG102"/>
   <sheetFormatPr defaultColWidth="9.140625" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="8.42578125" style="1" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="26.85546875" style="1" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="69.140625" style="1" bestFit="1" customWidth="1"/>
-    <col min="4" max="5" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="8" max="9" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="10" max="10" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
-    <col min="11" max="11" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="12" max="13" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="14" max="14" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
-    <col min="15" max="15" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="16" max="16" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="17" max="17" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="6" max="7" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="10" max="11" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="12" max="12" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
+    <col min="13" max="13" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="14" max="15" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="16" max="16" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
+    <col min="17" max="17" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
     <col min="18" max="18" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
     <col min="19" max="19" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
     <col min="20" max="20" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
@@ -687,109 +687,117 @@
     <col min="29" max="29" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
     <col min="30" max="30" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
     <col min="31" max="31" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
-    <col min="32" max="16384" width="9.140625" style="1"/>
+    <col min="32" max="32" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="33" max="33" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
+    <col min="34" max="16384" width="9.140625" style="1"/>
   </cols>
   <sheetData>
-    <row r="5" spans="1:31" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:33" x14ac:dyDescent="0.2">
       <c r="A5" s="1" t="s">
         <v>0</v>
       </c>
     </row>
-    <row r="6" spans="1:31" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:33" x14ac:dyDescent="0.2">
       <c r="B6" s="1" t="s">
         <v>1</v>
       </c>
     </row>
-    <row r="7" spans="1:31" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:33" x14ac:dyDescent="0.2">
       <c r="C7" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D7" s="2">
+        <v>46203</v>
+      </c>
+      <c r="E7" s="2">
+        <v>46112</v>
+      </c>
+      <c r="F7" s="2">
         <v>46022</v>
       </c>
-      <c r="E7" s="2">
+      <c r="G7" s="2">
         <v>45930</v>
       </c>
-      <c r="F7" s="2">
+      <c r="H7" s="2">
         <v>45838</v>
       </c>
-      <c r="G7" s="2">
+      <c r="I7" s="2">
         <v>45747</v>
       </c>
-      <c r="H7" s="2">
+      <c r="J7" s="2">
         <v>45657</v>
       </c>
-      <c r="I7" s="2">
+      <c r="K7" s="2">
         <v>45565</v>
       </c>
-      <c r="J7" s="2">
+      <c r="L7" s="2">
         <v>45473</v>
       </c>
-      <c r="K7" s="2">
+      <c r="M7" s="2">
         <v>45382</v>
       </c>
-      <c r="L7" s="2">
+      <c r="N7" s="2">
         <v>45291</v>
       </c>
-      <c r="M7" s="2">
+      <c r="O7" s="2">
         <v>45199</v>
       </c>
-      <c r="N7" s="2">
+      <c r="P7" s="2">
         <v>45107</v>
       </c>
-      <c r="O7" s="2">
+      <c r="Q7" s="2">
         <v>45016</v>
       </c>
-      <c r="P7" s="2">
+      <c r="R7" s="2">
         <v>44926</v>
       </c>
-      <c r="Q7" s="2">
+      <c r="S7" s="2">
         <v>44377</v>
       </c>
-      <c r="R7" s="2">
+      <c r="T7" s="2">
         <v>44196</v>
       </c>
-      <c r="S7" s="2">
+      <c r="U7" s="2">
         <v>44012</v>
       </c>
-      <c r="T7" s="2">
+      <c r="V7" s="2">
         <v>43830</v>
       </c>
-      <c r="U7" s="2">
+      <c r="W7" s="2">
         <v>43646</v>
       </c>
-      <c r="V7" s="2">
+      <c r="X7" s="2">
         <v>43465</v>
       </c>
-      <c r="W7" s="2">
+      <c r="Y7" s="2">
         <v>43281</v>
       </c>
-      <c r="X7" s="2">
+      <c r="Z7" s="2">
         <v>43100</v>
       </c>
-      <c r="Y7" s="2">
+      <c r="AA7" s="2">
         <v>42916</v>
       </c>
-      <c r="Z7" s="2">
+      <c r="AB7" s="2">
         <v>42735</v>
       </c>
-      <c r="AA7" s="2">
+      <c r="AC7" s="2">
         <v>42551</v>
       </c>
-      <c r="AB7" s="2">
+      <c r="AD7" s="2">
         <v>42369</v>
       </c>
-      <c r="AC7" s="2">
+      <c r="AE7" s="2">
         <v>42185</v>
       </c>
-      <c r="AD7" s="2">
+      <c r="AF7" s="2">
         <v>42004</v>
       </c>
-      <c r="AE7" s="2">
+      <c r="AG7" s="2">
         <v>41820</v>
       </c>
     </row>
-    <row r="8" spans="1:31" x14ac:dyDescent="0.2">
+    <row r="8" spans="1:33" x14ac:dyDescent="0.2">
       <c r="C8" s="1" t="s">
         <v>3</v>
       </c>
@@ -832,53 +840,59 @@
       <c r="P8" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="Q8" s="3">
+      <c r="Q8" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="R8" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="S8" s="3">
         <v>4226000</v>
       </c>
-      <c r="R8" s="3">
+      <c r="T8" s="3">
         <v>3692800</v>
       </c>
-      <c r="S8" s="3">
+      <c r="U8" s="3">
         <v>3437700</v>
       </c>
-      <c r="T8" s="3">
+      <c r="V8" s="3">
         <v>3493800</v>
       </c>
-      <c r="U8" s="3">
+      <c r="W8" s="3">
         <v>4091200</v>
       </c>
-      <c r="V8" s="3">
+      <c r="X8" s="3">
         <v>3897500</v>
       </c>
-      <c r="W8" s="3">
+      <c r="Y8" s="3">
         <v>3844900</v>
       </c>
-      <c r="X8" s="3">
+      <c r="Z8" s="3">
         <v>3724300</v>
       </c>
-      <c r="Y8" s="3">
+      <c r="AA8" s="3">
         <v>3572500</v>
       </c>
-      <c r="Z8" s="3">
+      <c r="AB8" s="3">
         <v>3343000</v>
       </c>
-      <c r="AA8" s="3">
+      <c r="AC8" s="3">
         <v>3436000</v>
       </c>
-      <c r="AB8" s="3">
+      <c r="AD8" s="3">
         <v>3107700</v>
       </c>
-      <c r="AC8" s="3">
+      <c r="AE8" s="3">
         <v>3329300</v>
       </c>
-      <c r="AD8" s="3">
+      <c r="AF8" s="3">
         <v>3229200</v>
       </c>
-      <c r="AE8" s="3">
+      <c r="AG8" s="3">
         <v>3392300</v>
       </c>
     </row>
-    <row r="9" spans="1:31" x14ac:dyDescent="0.2">
+    <row r="9" spans="1:33" x14ac:dyDescent="0.2">
       <c r="C9" s="1" t="s">
         <v>4</v>
       </c>
@@ -921,53 +935,59 @@
       <c r="P9" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="Q9" s="3">
+      <c r="Q9" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="R9" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="S9" s="3">
         <v>2855700</v>
       </c>
-      <c r="R9" s="3">
+      <c r="T9" s="3">
         <v>2456900</v>
       </c>
-      <c r="S9" s="3">
+      <c r="U9" s="3">
         <v>2365300</v>
       </c>
-      <c r="T9" s="3">
+      <c r="V9" s="3">
         <v>2440000</v>
       </c>
-      <c r="U9" s="3">
+      <c r="W9" s="3">
         <v>2861200</v>
       </c>
-      <c r="V9" s="3">
+      <c r="X9" s="3">
         <v>2839300</v>
       </c>
-      <c r="W9" s="3">
+      <c r="Y9" s="3">
         <v>2725300</v>
       </c>
-      <c r="X9" s="3">
+      <c r="Z9" s="3">
         <v>2638500</v>
       </c>
-      <c r="Y9" s="3">
+      <c r="AA9" s="3">
         <v>2505800</v>
       </c>
-      <c r="Z9" s="3">
+      <c r="AB9" s="3">
         <v>2334300</v>
       </c>
-      <c r="AA9" s="3">
+      <c r="AC9" s="3">
         <v>2440000</v>
       </c>
-      <c r="AB9" s="3">
+      <c r="AD9" s="3">
         <v>2248300</v>
       </c>
-      <c r="AC9" s="3">
+      <c r="AE9" s="3">
         <v>4753100</v>
       </c>
-      <c r="AD9" s="3">
+      <c r="AF9" s="3">
         <v>2349200</v>
       </c>
-      <c r="AE9" s="3">
+      <c r="AG9" s="3">
         <v>5005600</v>
       </c>
     </row>
-    <row r="10" spans="1:31" x14ac:dyDescent="0.2">
+    <row r="10" spans="1:33" x14ac:dyDescent="0.2">
       <c r="C10" s="1" t="s">
         <v>5</v>
       </c>
@@ -1010,53 +1030,59 @@
       <c r="P10" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="Q10" s="3">
+      <c r="Q10" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="R10" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="S10" s="3">
         <v>1370300</v>
       </c>
-      <c r="R10" s="3">
+      <c r="T10" s="3">
         <v>1235900</v>
       </c>
-      <c r="S10" s="3">
+      <c r="U10" s="3">
         <v>1072400</v>
       </c>
-      <c r="T10" s="3">
+      <c r="V10" s="3">
         <v>1053800</v>
       </c>
-      <c r="U10" s="3">
+      <c r="W10" s="3">
         <v>1230000</v>
       </c>
-      <c r="V10" s="3">
+      <c r="X10" s="3">
         <v>1058200</v>
       </c>
-      <c r="W10" s="3">
+      <c r="Y10" s="3">
         <v>1119600</v>
       </c>
-      <c r="X10" s="3">
+      <c r="Z10" s="3">
         <v>1085800</v>
       </c>
-      <c r="Y10" s="3">
+      <c r="AA10" s="3">
         <v>1066700</v>
       </c>
-      <c r="Z10" s="3">
+      <c r="AB10" s="3">
         <v>1008700</v>
       </c>
-      <c r="AA10" s="3">
+      <c r="AC10" s="3">
         <v>996000</v>
       </c>
-      <c r="AB10" s="3">
+      <c r="AD10" s="3">
         <v>859400</v>
       </c>
-      <c r="AC10" s="3">
+      <c r="AE10" s="3">
         <v>-1423800</v>
       </c>
-      <c r="AD10" s="3">
+      <c r="AF10" s="3">
         <v>880000</v>
       </c>
-      <c r="AE10" s="3">
+      <c r="AG10" s="3">
         <v>-1613300</v>
       </c>
     </row>
-    <row r="11" spans="1:31" x14ac:dyDescent="0.2">
+    <row r="11" spans="1:33" x14ac:dyDescent="0.2">
       <c r="C11" s="1" t="s">
         <v>6</v>
       </c>
@@ -1088,8 +1114,10 @@
       <c r="AC11" s="3"/>
       <c r="AD11" s="3"/>
       <c r="AE11" s="3"/>
-    </row>
-    <row r="12" spans="1:31" x14ac:dyDescent="0.2">
+      <c r="AF11" s="3"/>
+      <c r="AG11" s="3"/>
+    </row>
+    <row r="12" spans="1:33" x14ac:dyDescent="0.2">
       <c r="C12" s="1" t="s">
         <v>7</v>
       </c>
@@ -1177,8 +1205,14 @@
       <c r="AE12" s="3" t="s">
         <v>8</v>
       </c>
-    </row>
-    <row r="13" spans="1:31" x14ac:dyDescent="0.2">
+      <c r="AF12" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="AG12" s="3" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="13" spans="1:33" x14ac:dyDescent="0.2">
       <c r="C13" s="1" t="s">
         <v>9</v>
       </c>
@@ -1266,8 +1300,14 @@
       <c r="AE13" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="14" spans="1:31" x14ac:dyDescent="0.2">
+      <c r="AF13" s="3">
+        <v>0</v>
+      </c>
+      <c r="AG13" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="14" spans="1:33" x14ac:dyDescent="0.2">
       <c r="C14" s="1" t="s">
         <v>10</v>
       </c>
@@ -1310,32 +1350,32 @@
       <c r="P14" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="Q14" s="3">
+      <c r="Q14" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="R14" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="S14" s="3">
         <v>11300</v>
       </c>
-      <c r="R14" s="3">
+      <c r="T14" s="3">
         <v>-9500</v>
       </c>
-      <c r="S14" s="3">
+      <c r="U14" s="3">
         <v>94400</v>
       </c>
-      <c r="T14" s="3">
+      <c r="V14" s="3">
         <v>242300</v>
       </c>
-      <c r="U14" s="3">
+      <c r="W14" s="3">
         <v>280000</v>
       </c>
-      <c r="V14" s="3">
+      <c r="X14" s="3">
         <v>96400</v>
       </c>
-      <c r="W14" s="3">
-        <v>0</v>
-      </c>
-      <c r="X14" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="Y14" s="3" t="s">
-        <v>8</v>
+      <c r="Y14" s="3">
+        <v>0</v>
       </c>
       <c r="Z14" s="3" t="s">
         <v>8</v>
@@ -1343,11 +1383,11 @@
       <c r="AA14" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="AB14" s="3">
-        <v>0</v>
-      </c>
-      <c r="AC14" s="3">
-        <v>0</v>
+      <c r="AB14" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="AC14" s="3" t="s">
+        <v>8</v>
       </c>
       <c r="AD14" s="3">
         <v>0</v>
@@ -1355,8 +1395,14 @@
       <c r="AE14" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="15" spans="1:31" x14ac:dyDescent="0.2">
+      <c r="AF14" s="3">
+        <v>0</v>
+      </c>
+      <c r="AG14" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="15" spans="1:33" x14ac:dyDescent="0.2">
       <c r="C15" s="1" t="s">
         <v>11</v>
       </c>
@@ -1411,11 +1457,11 @@
       <c r="T15" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="U15" s="3">
-        <v>0</v>
-      </c>
-      <c r="V15" s="3">
-        <v>0</v>
+      <c r="U15" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="V15" s="3" t="s">
+        <v>8</v>
       </c>
       <c r="W15" s="3">
         <v>0</v>
@@ -1444,8 +1490,14 @@
       <c r="AE15" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="16" spans="1:31" x14ac:dyDescent="0.2">
+      <c r="AF15" s="3">
+        <v>0</v>
+      </c>
+      <c r="AG15" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="16" spans="1:33" x14ac:dyDescent="0.2">
       <c r="D16" s="3"/>
       <c r="E16" s="3"/>
       <c r="F16" s="3"/>
@@ -1474,8 +1526,10 @@
       <c r="AC16" s="3"/>
       <c r="AD16" s="3"/>
       <c r="AE16" s="3"/>
-    </row>
-    <row r="17" spans="3:31" x14ac:dyDescent="0.2">
+      <c r="AF16" s="3"/>
+      <c r="AG16" s="3"/>
+    </row>
+    <row r="17" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C17" s="1" t="s">
         <v>12</v>
       </c>
@@ -1518,53 +1572,59 @@
       <c r="P17" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="Q17" s="3">
+      <c r="Q17" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="R17" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="S17" s="3">
         <v>3631600</v>
       </c>
-      <c r="R17" s="3">
+      <c r="T17" s="3">
         <v>3090800</v>
       </c>
-      <c r="S17" s="3">
+      <c r="U17" s="3">
         <v>3005800</v>
       </c>
-      <c r="T17" s="3">
+      <c r="V17" s="3">
         <v>3306400</v>
       </c>
-      <c r="U17" s="3">
+      <c r="W17" s="3">
         <v>3763600</v>
       </c>
-      <c r="V17" s="3">
+      <c r="X17" s="3">
         <v>3480900</v>
       </c>
-      <c r="W17" s="3">
+      <c r="Y17" s="3">
         <v>3322000</v>
       </c>
-      <c r="X17" s="3">
+      <c r="Z17" s="3">
         <v>3259700</v>
       </c>
-      <c r="Y17" s="3">
+      <c r="AA17" s="3">
         <v>3026300</v>
       </c>
-      <c r="Z17" s="3">
+      <c r="AB17" s="3">
         <v>2971500</v>
       </c>
-      <c r="AA17" s="3">
+      <c r="AC17" s="3">
         <v>2938000</v>
       </c>
-      <c r="AB17" s="3">
+      <c r="AD17" s="3">
         <v>2836800</v>
       </c>
-      <c r="AC17" s="3">
+      <c r="AE17" s="3">
         <v>2941400</v>
       </c>
-      <c r="AD17" s="3">
+      <c r="AF17" s="3">
         <v>3119200</v>
       </c>
-      <c r="AE17" s="3">
+      <c r="AG17" s="3">
         <v>2908900</v>
       </c>
     </row>
-    <row r="18" spans="3:31" x14ac:dyDescent="0.2">
+    <row r="18" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C18" s="1" t="s">
         <v>13</v>
       </c>
@@ -1607,53 +1667,59 @@
       <c r="P18" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="Q18" s="3">
+      <c r="Q18" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="R18" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="S18" s="3">
         <v>594400</v>
       </c>
-      <c r="R18" s="3">
+      <c r="T18" s="3">
         <v>602000</v>
       </c>
-      <c r="S18" s="3">
+      <c r="U18" s="3">
         <v>431900</v>
       </c>
-      <c r="T18" s="3">
+      <c r="V18" s="3">
         <v>187400</v>
       </c>
-      <c r="U18" s="3">
+      <c r="W18" s="3">
         <v>327600</v>
       </c>
-      <c r="V18" s="3">
+      <c r="X18" s="3">
         <v>416600</v>
       </c>
-      <c r="W18" s="3">
+      <c r="Y18" s="3">
         <v>522900</v>
       </c>
-      <c r="X18" s="3">
+      <c r="Z18" s="3">
         <v>464600</v>
       </c>
-      <c r="Y18" s="3">
+      <c r="AA18" s="3">
         <v>546200</v>
       </c>
-      <c r="Z18" s="3">
+      <c r="AB18" s="3">
         <v>371500</v>
       </c>
-      <c r="AA18" s="3">
+      <c r="AC18" s="3">
         <v>498000</v>
       </c>
-      <c r="AB18" s="3">
+      <c r="AD18" s="3">
         <v>270900</v>
       </c>
-      <c r="AC18" s="3">
+      <c r="AE18" s="3">
         <v>387900</v>
       </c>
-      <c r="AD18" s="3">
+      <c r="AF18" s="3">
         <v>110000</v>
       </c>
-      <c r="AE18" s="3">
+      <c r="AG18" s="3">
         <v>483400</v>
       </c>
     </row>
-    <row r="19" spans="3:31" x14ac:dyDescent="0.2">
+    <row r="19" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C19" s="1" t="s">
         <v>14</v>
       </c>
@@ -1685,8 +1751,10 @@
       <c r="AC19" s="3"/>
       <c r="AD19" s="3"/>
       <c r="AE19" s="3"/>
-    </row>
-    <row r="20" spans="3:31" x14ac:dyDescent="0.2">
+      <c r="AF19" s="3"/>
+      <c r="AG19" s="3"/>
+    </row>
+    <row r="20" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C20" s="1" t="s">
         <v>15</v>
       </c>
@@ -1729,53 +1797,59 @@
       <c r="P20" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="Q20" s="3">
+      <c r="Q20" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="R20" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="S20" s="3">
         <v>187100</v>
       </c>
-      <c r="R20" s="3">
+      <c r="T20" s="3">
         <v>162400</v>
       </c>
-      <c r="S20" s="3">
+      <c r="U20" s="3">
         <v>186400</v>
       </c>
-      <c r="T20" s="3">
+      <c r="V20" s="3">
         <v>197500</v>
       </c>
-      <c r="U20" s="3">
+      <c r="W20" s="3">
         <v>206200</v>
       </c>
-      <c r="V20" s="3">
+      <c r="X20" s="3">
         <v>166000</v>
       </c>
-      <c r="W20" s="3">
+      <c r="Y20" s="3">
         <v>218100</v>
       </c>
-      <c r="X20" s="3">
+      <c r="Z20" s="3">
         <v>100900</v>
       </c>
-      <c r="Y20" s="3">
+      <c r="AA20" s="3">
         <v>159000</v>
       </c>
-      <c r="Z20" s="3">
+      <c r="AB20" s="3">
         <v>127900</v>
       </c>
-      <c r="AA20" s="3">
+      <c r="AC20" s="3">
         <v>152900</v>
       </c>
-      <c r="AB20" s="3">
+      <c r="AD20" s="3">
         <v>103400</v>
       </c>
-      <c r="AC20" s="3">
+      <c r="AE20" s="3">
         <v>204500</v>
       </c>
-      <c r="AD20" s="3">
+      <c r="AF20" s="3">
         <v>172700</v>
       </c>
-      <c r="AE20" s="3">
+      <c r="AG20" s="3">
         <v>189300</v>
       </c>
     </row>
-    <row r="21" spans="3:31" x14ac:dyDescent="0.2">
+    <row r="21" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C21" s="1" t="s">
         <v>16</v>
       </c>
@@ -1818,53 +1892,59 @@
       <c r="P21" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="Q21" s="3">
+      <c r="Q21" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="R21" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="S21" s="3">
         <v>1027800</v>
       </c>
-      <c r="R21" s="3">
+      <c r="T21" s="3">
         <v>1058700</v>
       </c>
-      <c r="S21" s="3">
+      <c r="U21" s="3">
         <v>876900</v>
       </c>
-      <c r="T21" s="3">
+      <c r="V21" s="3">
         <v>660300</v>
       </c>
-      <c r="U21" s="3">
+      <c r="W21" s="3">
         <v>791600</v>
       </c>
-      <c r="V21" s="3">
+      <c r="X21" s="3">
         <v>834500</v>
       </c>
-      <c r="W21" s="3">
+      <c r="Y21" s="3">
         <v>950200</v>
       </c>
-      <c r="X21" s="3">
+      <c r="Z21" s="3">
         <v>809200</v>
       </c>
-      <c r="Y21" s="3">
+      <c r="AA21" s="3">
         <v>882700</v>
       </c>
-      <c r="Z21" s="3">
+      <c r="AB21" s="3">
         <v>682900</v>
       </c>
-      <c r="AA21" s="3">
+      <c r="AC21" s="3">
         <v>833200</v>
       </c>
-      <c r="AB21" s="3">
+      <c r="AD21" s="3">
         <v>563900</v>
       </c>
-      <c r="AC21" s="3">
+      <c r="AE21" s="3">
         <v>766900</v>
       </c>
-      <c r="AD21" s="3">
+      <c r="AF21" s="3">
         <v>454400</v>
       </c>
-      <c r="AE21" s="3">
+      <c r="AG21" s="3">
         <v>820500</v>
       </c>
     </row>
-    <row r="22" spans="3:31" x14ac:dyDescent="0.2">
+    <row r="22" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C22" s="1" t="s">
         <v>17</v>
       </c>
@@ -1907,53 +1987,59 @@
       <c r="P22" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="Q22" s="3">
+      <c r="Q22" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="R22" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="S22" s="3">
         <v>233900</v>
       </c>
-      <c r="R22" s="3">
+      <c r="T22" s="3">
         <v>237200</v>
       </c>
-      <c r="S22" s="3">
+      <c r="U22" s="3">
         <v>205400</v>
       </c>
-      <c r="T22" s="3">
+      <c r="V22" s="3">
         <v>201800</v>
       </c>
-      <c r="U22" s="3">
+      <c r="W22" s="3">
         <v>236400</v>
       </c>
-      <c r="V22" s="3">
+      <c r="X22" s="3">
         <v>226900</v>
       </c>
-      <c r="W22" s="3">
+      <c r="Y22" s="3">
         <v>195400</v>
       </c>
-      <c r="X22" s="3">
+      <c r="Z22" s="3">
         <v>217500</v>
       </c>
-      <c r="Y22" s="3">
+      <c r="AA22" s="3">
         <v>169000</v>
       </c>
-      <c r="Z22" s="3">
+      <c r="AB22" s="3">
         <v>179800</v>
       </c>
-      <c r="AA22" s="3">
+      <c r="AC22" s="3">
         <v>186400</v>
       </c>
-      <c r="AB22" s="3">
+      <c r="AD22" s="3">
         <v>196200</v>
       </c>
-      <c r="AC22" s="3">
+      <c r="AE22" s="3">
         <v>178600</v>
       </c>
-      <c r="AD22" s="3">
+      <c r="AF22" s="3">
         <v>183500</v>
       </c>
-      <c r="AE22" s="3">
+      <c r="AG22" s="3">
         <v>167600</v>
       </c>
     </row>
-    <row r="23" spans="3:31" x14ac:dyDescent="0.2">
+    <row r="23" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C23" s="1" t="s">
         <v>18</v>
       </c>
@@ -1996,53 +2082,59 @@
       <c r="P23" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="Q23" s="3">
+      <c r="Q23" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="R23" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="S23" s="3">
         <v>547600</v>
       </c>
-      <c r="R23" s="3">
+      <c r="T23" s="3">
         <v>527200</v>
       </c>
-      <c r="S23" s="3">
+      <c r="U23" s="3">
         <v>412900</v>
       </c>
-      <c r="T23" s="3">
+      <c r="V23" s="3">
         <v>183100</v>
       </c>
-      <c r="U23" s="3">
+      <c r="W23" s="3">
         <v>297400</v>
       </c>
-      <c r="V23" s="3">
+      <c r="X23" s="3">
         <v>355700</v>
       </c>
-      <c r="W23" s="3">
+      <c r="Y23" s="3">
         <v>545600</v>
       </c>
-      <c r="X23" s="3">
+      <c r="Z23" s="3">
         <v>348000</v>
       </c>
-      <c r="Y23" s="3">
+      <c r="AA23" s="3">
         <v>536200</v>
       </c>
-      <c r="Z23" s="3">
+      <c r="AB23" s="3">
         <v>319600</v>
       </c>
-      <c r="AA23" s="3">
+      <c r="AC23" s="3">
         <v>464500</v>
       </c>
-      <c r="AB23" s="3">
+      <c r="AD23" s="3">
         <v>178100</v>
       </c>
-      <c r="AC23" s="3">
+      <c r="AE23" s="3">
         <v>413800</v>
       </c>
-      <c r="AD23" s="3">
+      <c r="AF23" s="3">
         <v>99200</v>
       </c>
-      <c r="AE23" s="3">
+      <c r="AG23" s="3">
         <v>505100</v>
       </c>
     </row>
-    <row r="24" spans="3:31" x14ac:dyDescent="0.2">
+    <row r="24" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C24" s="1" t="s">
         <v>19</v>
       </c>
@@ -2085,53 +2177,59 @@
       <c r="P24" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="Q24" s="3">
+      <c r="Q24" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="R24" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="S24" s="3">
         <v>140700</v>
       </c>
-      <c r="R24" s="3">
+      <c r="T24" s="3">
         <v>189700</v>
       </c>
-      <c r="S24" s="3">
+      <c r="U24" s="3">
         <v>151900</v>
       </c>
-      <c r="T24" s="3">
+      <c r="V24" s="3">
         <v>277200</v>
       </c>
-      <c r="U24" s="3">
+      <c r="W24" s="3">
         <v>167200</v>
       </c>
-      <c r="V24" s="3">
+      <c r="X24" s="3">
         <v>155900</v>
       </c>
-      <c r="W24" s="3">
+      <c r="Y24" s="3">
         <v>136700</v>
       </c>
-      <c r="X24" s="3">
+      <c r="Z24" s="3">
         <v>181600</v>
       </c>
-      <c r="Y24" s="3">
+      <c r="AA24" s="3">
         <v>141300</v>
       </c>
-      <c r="Z24" s="3">
+      <c r="AB24" s="3">
         <v>173100</v>
       </c>
-      <c r="AA24" s="3">
+      <c r="AC24" s="3">
         <v>113200</v>
       </c>
-      <c r="AB24" s="3">
+      <c r="AD24" s="3">
         <v>105200</v>
       </c>
-      <c r="AC24" s="3">
+      <c r="AE24" s="3">
         <v>85300</v>
       </c>
-      <c r="AD24" s="3">
+      <c r="AF24" s="3">
         <v>84000</v>
       </c>
-      <c r="AE24" s="3">
+      <c r="AG24" s="3">
         <v>103700</v>
       </c>
     </row>
-    <row r="25" spans="3:31" x14ac:dyDescent="0.2">
+    <row r="25" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C25" s="1" t="s">
         <v>20</v>
       </c>
@@ -2219,8 +2317,14 @@
       <c r="AE25" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="26" spans="3:31" x14ac:dyDescent="0.2">
+      <c r="AF25" s="3">
+        <v>0</v>
+      </c>
+      <c r="AG25" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="26" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C26" s="1" t="s">
         <v>21</v>
       </c>
@@ -2263,53 +2367,59 @@
       <c r="P26" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="Q26" s="3">
+      <c r="Q26" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="R26" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="S26" s="3">
         <v>406900</v>
       </c>
-      <c r="R26" s="3">
+      <c r="T26" s="3">
         <v>337500</v>
       </c>
-      <c r="S26" s="3">
+      <c r="U26" s="3">
         <v>261000</v>
       </c>
-      <c r="T26" s="3">
+      <c r="V26" s="3">
         <v>-94100</v>
       </c>
-      <c r="U26" s="3">
+      <c r="W26" s="3">
         <v>130200</v>
       </c>
-      <c r="V26" s="3">
+      <c r="X26" s="3">
         <v>199800</v>
       </c>
-      <c r="W26" s="3">
+      <c r="Y26" s="3">
         <v>408900</v>
       </c>
-      <c r="X26" s="3">
+      <c r="Z26" s="3">
         <v>166400</v>
       </c>
-      <c r="Y26" s="3">
+      <c r="AA26" s="3">
         <v>394900</v>
       </c>
-      <c r="Z26" s="3">
+      <c r="AB26" s="3">
         <v>146500</v>
       </c>
-      <c r="AA26" s="3">
+      <c r="AC26" s="3">
         <v>351300</v>
       </c>
-      <c r="AB26" s="3">
+      <c r="AD26" s="3">
         <v>72900</v>
       </c>
-      <c r="AC26" s="3">
+      <c r="AE26" s="3">
         <v>328500</v>
       </c>
-      <c r="AD26" s="3">
+      <c r="AF26" s="3">
         <v>15200</v>
       </c>
-      <c r="AE26" s="3">
+      <c r="AG26" s="3">
         <v>401400</v>
       </c>
     </row>
-    <row r="27" spans="3:31" x14ac:dyDescent="0.2">
+    <row r="27" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C27" s="1" t="s">
         <v>22</v>
       </c>
@@ -2352,53 +2462,59 @@
       <c r="P27" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="Q27" s="3">
+      <c r="Q27" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="R27" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="S27" s="3">
         <v>90300</v>
       </c>
-      <c r="R27" s="3">
+      <c r="T27" s="3">
         <v>69800</v>
       </c>
-      <c r="S27" s="3">
+      <c r="U27" s="3">
         <v>62700</v>
       </c>
-      <c r="T27" s="3">
+      <c r="V27" s="3">
         <v>-190600</v>
       </c>
-      <c r="U27" s="3">
+      <c r="W27" s="3">
         <v>-148300</v>
       </c>
-      <c r="V27" s="3">
+      <c r="X27" s="3">
         <v>-2000</v>
       </c>
-      <c r="W27" s="3">
+      <c r="Y27" s="3">
         <v>133800</v>
       </c>
-      <c r="X27" s="3">
+      <c r="Z27" s="3">
         <v>-12200</v>
       </c>
-      <c r="Y27" s="3">
+      <c r="AA27" s="3">
         <v>133100</v>
       </c>
-      <c r="Z27" s="3">
+      <c r="AB27" s="3">
         <v>-26000</v>
       </c>
-      <c r="AA27" s="3">
+      <c r="AC27" s="3">
         <v>121900</v>
       </c>
-      <c r="AB27" s="3">
+      <c r="AD27" s="3">
         <v>-73400</v>
       </c>
-      <c r="AC27" s="3">
+      <c r="AE27" s="3">
         <v>145400</v>
       </c>
-      <c r="AD27" s="3">
+      <c r="AF27" s="3">
         <v>-131500</v>
       </c>
-      <c r="AE27" s="3">
+      <c r="AG27" s="3">
         <v>169300</v>
       </c>
     </row>
-    <row r="28" spans="3:31" x14ac:dyDescent="0.2">
+    <row r="28" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C28" s="1" t="s">
         <v>23</v>
       </c>
@@ -2486,8 +2602,14 @@
       <c r="AE28" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="29" spans="3:31" x14ac:dyDescent="0.2">
+      <c r="AF28" s="3">
+        <v>0</v>
+      </c>
+      <c r="AG28" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="29" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C29" s="1" t="s">
         <v>24</v>
       </c>
@@ -2530,53 +2652,59 @@
       <c r="P29" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="Q29" s="3">
+      <c r="Q29" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="R29" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="S29" s="3">
         <v>90700</v>
       </c>
-      <c r="R29" s="3">
+      <c r="T29" s="3">
         <v>31200</v>
       </c>
-      <c r="S29" s="3">
+      <c r="U29" s="3">
         <v>37900</v>
       </c>
-      <c r="T29" s="3">
+      <c r="V29" s="3">
         <v>85000</v>
       </c>
-      <c r="U29" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="V29" s="3" t="s">
-        <v>8</v>
-      </c>
       <c r="W29" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="X29" s="3">
-        <v>0</v>
-      </c>
-      <c r="Y29" s="3">
-        <v>0</v>
+      <c r="X29" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="Y29" s="3" t="s">
+        <v>8</v>
       </c>
       <c r="Z29" s="3">
+        <v>0</v>
+      </c>
+      <c r="AA29" s="3">
+        <v>0</v>
+      </c>
+      <c r="AB29" s="3">
         <v>1600</v>
       </c>
-      <c r="AA29" s="3">
+      <c r="AC29" s="3">
         <v>5700</v>
       </c>
-      <c r="AB29" s="3">
+      <c r="AD29" s="3">
         <v>-1100</v>
       </c>
-      <c r="AC29" s="3">
+      <c r="AE29" s="3">
         <v>12000</v>
       </c>
-      <c r="AD29" s="3">
+      <c r="AF29" s="3">
         <v>26200</v>
       </c>
-      <c r="AE29" s="3">
+      <c r="AG29" s="3">
         <v>17000</v>
       </c>
     </row>
-    <row r="30" spans="3:31" x14ac:dyDescent="0.2">
+    <row r="30" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C30" s="1" t="s">
         <v>25</v>
       </c>
@@ -2664,8 +2792,14 @@
       <c r="AE30" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="31" spans="3:31" x14ac:dyDescent="0.2">
+      <c r="AF30" s="3">
+        <v>0</v>
+      </c>
+      <c r="AG30" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="31" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C31" s="1" t="s">
         <v>26</v>
       </c>
@@ -2753,8 +2887,14 @@
       <c r="AE31" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="32" spans="3:31" x14ac:dyDescent="0.2">
+      <c r="AF31" s="3">
+        <v>0</v>
+      </c>
+      <c r="AG31" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="32" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C32" s="1" t="s">
         <v>27</v>
       </c>
@@ -2797,53 +2937,59 @@
       <c r="P32" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="Q32" s="3">
+      <c r="Q32" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="R32" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="S32" s="3">
         <v>-187100</v>
       </c>
-      <c r="R32" s="3">
+      <c r="T32" s="3">
         <v>-162400</v>
       </c>
-      <c r="S32" s="3">
+      <c r="U32" s="3">
         <v>-186400</v>
       </c>
-      <c r="T32" s="3">
+      <c r="V32" s="3">
         <v>-197500</v>
       </c>
-      <c r="U32" s="3">
+      <c r="W32" s="3">
         <v>-206200</v>
       </c>
-      <c r="V32" s="3">
+      <c r="X32" s="3">
         <v>-166000</v>
       </c>
-      <c r="W32" s="3">
+      <c r="Y32" s="3">
         <v>-218100</v>
       </c>
-      <c r="X32" s="3">
+      <c r="Z32" s="3">
         <v>-100900</v>
       </c>
-      <c r="Y32" s="3">
+      <c r="AA32" s="3">
         <v>-159000</v>
       </c>
-      <c r="Z32" s="3">
+      <c r="AB32" s="3">
         <v>-127900</v>
       </c>
-      <c r="AA32" s="3">
+      <c r="AC32" s="3">
         <v>-152900</v>
       </c>
-      <c r="AB32" s="3">
+      <c r="AD32" s="3">
         <v>-103400</v>
       </c>
-      <c r="AC32" s="3">
+      <c r="AE32" s="3">
         <v>-204500</v>
       </c>
-      <c r="AD32" s="3">
+      <c r="AF32" s="3">
         <v>-172700</v>
       </c>
-      <c r="AE32" s="3">
+      <c r="AG32" s="3">
         <v>-189300</v>
       </c>
     </row>
-    <row r="33" spans="2:31" x14ac:dyDescent="0.2">
+    <row r="33" spans="2:33" x14ac:dyDescent="0.2">
       <c r="C33" s="1" t="s">
         <v>28</v>
       </c>
@@ -2886,53 +3032,59 @@
       <c r="P33" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="Q33" s="3">
+      <c r="Q33" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="R33" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="S33" s="3">
         <v>181000</v>
       </c>
-      <c r="R33" s="3">
+      <c r="T33" s="3">
         <v>101000</v>
       </c>
-      <c r="S33" s="3">
+      <c r="U33" s="3">
         <v>100600</v>
       </c>
-      <c r="T33" s="3">
+      <c r="V33" s="3">
         <v>-105600</v>
       </c>
-      <c r="U33" s="3">
+      <c r="W33" s="3">
         <v>-148300</v>
       </c>
-      <c r="V33" s="3">
+      <c r="X33" s="3">
         <v>-2000</v>
       </c>
-      <c r="W33" s="3">
+      <c r="Y33" s="3">
         <v>133800</v>
       </c>
-      <c r="X33" s="3">
+      <c r="Z33" s="3">
         <v>-12200</v>
       </c>
-      <c r="Y33" s="3">
+      <c r="AA33" s="3">
         <v>133100</v>
       </c>
-      <c r="Z33" s="3">
+      <c r="AB33" s="3">
         <v>-24400</v>
       </c>
-      <c r="AA33" s="3">
+      <c r="AC33" s="3">
         <v>127600</v>
       </c>
-      <c r="AB33" s="3">
+      <c r="AD33" s="3">
         <v>-74500</v>
       </c>
-      <c r="AC33" s="3">
+      <c r="AE33" s="3">
         <v>157400</v>
       </c>
-      <c r="AD33" s="3">
+      <c r="AF33" s="3">
         <v>-105300</v>
       </c>
-      <c r="AE33" s="3">
+      <c r="AG33" s="3">
         <v>186300</v>
       </c>
     </row>
-    <row r="34" spans="2:31" x14ac:dyDescent="0.2">
+    <row r="34" spans="2:33" x14ac:dyDescent="0.2">
       <c r="C34" s="1" t="s">
         <v>29</v>
       </c>
@@ -3020,8 +3172,14 @@
       <c r="AE34" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="35" spans="2:31" x14ac:dyDescent="0.2">
+      <c r="AF34" s="3">
+        <v>0</v>
+      </c>
+      <c r="AG34" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="35" spans="2:33" x14ac:dyDescent="0.2">
       <c r="C35" s="1" t="s">
         <v>30</v>
       </c>
@@ -3064,147 +3222,159 @@
       <c r="P35" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="Q35" s="3">
+      <c r="Q35" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="R35" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="S35" s="3">
         <v>181000</v>
       </c>
-      <c r="R35" s="3">
+      <c r="T35" s="3">
         <v>101000</v>
       </c>
-      <c r="S35" s="3">
+      <c r="U35" s="3">
         <v>100600</v>
       </c>
-      <c r="T35" s="3">
+      <c r="V35" s="3">
         <v>-105600</v>
       </c>
-      <c r="U35" s="3">
+      <c r="W35" s="3">
         <v>-148300</v>
       </c>
-      <c r="V35" s="3">
+      <c r="X35" s="3">
         <v>-2000</v>
       </c>
-      <c r="W35" s="3">
+      <c r="Y35" s="3">
         <v>133800</v>
       </c>
-      <c r="X35" s="3">
+      <c r="Z35" s="3">
         <v>-12200</v>
       </c>
-      <c r="Y35" s="3">
+      <c r="AA35" s="3">
         <v>133100</v>
       </c>
-      <c r="Z35" s="3">
+      <c r="AB35" s="3">
         <v>-24400</v>
       </c>
-      <c r="AA35" s="3">
+      <c r="AC35" s="3">
         <v>127600</v>
       </c>
-      <c r="AB35" s="3">
+      <c r="AD35" s="3">
         <v>-74500</v>
       </c>
-      <c r="AC35" s="3">
+      <c r="AE35" s="3">
         <v>157400</v>
       </c>
-      <c r="AD35" s="3">
+      <c r="AF35" s="3">
         <v>-105300</v>
       </c>
-      <c r="AE35" s="3">
+      <c r="AG35" s="3">
         <v>186300</v>
       </c>
     </row>
-    <row r="37" spans="2:31" x14ac:dyDescent="0.2">
+    <row r="37" spans="2:33" x14ac:dyDescent="0.2">
       <c r="B37" s="1" t="s">
         <v>31</v>
       </c>
     </row>
-    <row r="38" spans="2:31" x14ac:dyDescent="0.2">
+    <row r="38" spans="2:33" x14ac:dyDescent="0.2">
       <c r="C38" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D38" s="2">
+        <v>46203</v>
+      </c>
+      <c r="E38" s="2">
+        <v>46112</v>
+      </c>
+      <c r="F38" s="2">
         <v>46022</v>
       </c>
-      <c r="E38" s="2">
+      <c r="G38" s="2">
         <v>45930</v>
       </c>
-      <c r="F38" s="2">
+      <c r="H38" s="2">
         <v>45838</v>
       </c>
-      <c r="G38" s="2">
+      <c r="I38" s="2">
         <v>45747</v>
       </c>
-      <c r="H38" s="2">
+      <c r="J38" s="2">
         <v>45657</v>
       </c>
-      <c r="I38" s="2">
+      <c r="K38" s="2">
         <v>45565</v>
       </c>
-      <c r="J38" s="2">
+      <c r="L38" s="2">
         <v>45473</v>
       </c>
-      <c r="K38" s="2">
+      <c r="M38" s="2">
         <v>45382</v>
       </c>
-      <c r="L38" s="2">
+      <c r="N38" s="2">
         <v>45291</v>
       </c>
-      <c r="M38" s="2">
+      <c r="O38" s="2">
         <v>45199</v>
       </c>
-      <c r="N38" s="2">
+      <c r="P38" s="2">
         <v>45107</v>
       </c>
-      <c r="O38" s="2">
+      <c r="Q38" s="2">
         <v>45016</v>
       </c>
-      <c r="P38" s="2">
+      <c r="R38" s="2">
         <v>44926</v>
       </c>
-      <c r="Q38" s="2">
+      <c r="S38" s="2">
         <v>44377</v>
       </c>
-      <c r="R38" s="2">
+      <c r="T38" s="2">
         <v>44196</v>
       </c>
-      <c r="S38" s="2">
+      <c r="U38" s="2">
         <v>44012</v>
       </c>
-      <c r="T38" s="2">
+      <c r="V38" s="2">
         <v>43830</v>
       </c>
-      <c r="U38" s="2">
+      <c r="W38" s="2">
         <v>43646</v>
       </c>
-      <c r="V38" s="2">
+      <c r="X38" s="2">
         <v>43465</v>
       </c>
-      <c r="W38" s="2">
+      <c r="Y38" s="2">
         <v>43281</v>
       </c>
-      <c r="X38" s="2">
+      <c r="Z38" s="2">
         <v>43100</v>
       </c>
-      <c r="Y38" s="2">
+      <c r="AA38" s="2">
         <v>42916</v>
       </c>
-      <c r="Z38" s="2">
+      <c r="AB38" s="2">
         <v>42735</v>
       </c>
-      <c r="AA38" s="2">
+      <c r="AC38" s="2">
         <v>42551</v>
       </c>
-      <c r="AB38" s="2">
+      <c r="AD38" s="2">
         <v>42369</v>
       </c>
-      <c r="AC38" s="2">
+      <c r="AE38" s="2">
         <v>42185</v>
       </c>
-      <c r="AD38" s="2">
+      <c r="AF38" s="2">
         <v>42004</v>
       </c>
-      <c r="AE38" s="2">
+      <c r="AG38" s="2">
         <v>41820</v>
       </c>
     </row>
-    <row r="39" spans="2:31" x14ac:dyDescent="0.2">
+    <row r="39" spans="2:33" x14ac:dyDescent="0.2">
       <c r="C39" s="1" t="s">
         <v>32</v>
       </c>
@@ -3236,8 +3406,10 @@
       <c r="AC39" s="3"/>
       <c r="AD39" s="3"/>
       <c r="AE39" s="3"/>
-    </row>
-    <row r="40" spans="2:31" x14ac:dyDescent="0.2">
+      <c r="AF39" s="3"/>
+      <c r="AG39" s="3"/>
+    </row>
+    <row r="40" spans="2:33" x14ac:dyDescent="0.2">
       <c r="C40" s="1" t="s">
         <v>33</v>
       </c>
@@ -3269,809 +3441,865 @@
       <c r="AC40" s="3"/>
       <c r="AD40" s="3"/>
       <c r="AE40" s="3"/>
-    </row>
-    <row r="41" spans="2:31" x14ac:dyDescent="0.2">
+      <c r="AF40" s="3"/>
+      <c r="AG40" s="3"/>
+    </row>
+    <row r="41" spans="2:33" x14ac:dyDescent="0.2">
       <c r="C41" s="1" t="s">
         <v>34</v>
       </c>
       <c r="D41" s="3">
+        <v>4383600</v>
+      </c>
+      <c r="E41" s="3">
+        <v>4383600</v>
+      </c>
+      <c r="F41" s="3">
         <v>3381000</v>
       </c>
-      <c r="E41" s="3">
+      <c r="G41" s="3">
         <v>3381000</v>
       </c>
-      <c r="F41" s="3">
+      <c r="H41" s="3">
         <v>3557900</v>
       </c>
-      <c r="G41" s="3">
+      <c r="I41" s="3">
         <v>3557900</v>
       </c>
-      <c r="H41" s="3">
+      <c r="J41" s="3">
         <v>2857000</v>
       </c>
-      <c r="I41" s="3">
+      <c r="K41" s="3">
         <v>2857000</v>
       </c>
-      <c r="J41" s="3">
+      <c r="L41" s="3">
         <v>3026000</v>
       </c>
-      <c r="K41" s="3">
+      <c r="M41" s="3">
         <v>3026000</v>
       </c>
-      <c r="L41" s="3">
+      <c r="N41" s="3">
         <v>2349700</v>
       </c>
-      <c r="M41" s="3">
+      <c r="O41" s="3">
         <v>2349700</v>
       </c>
-      <c r="N41" s="3">
+      <c r="P41" s="3">
         <v>2700000</v>
       </c>
-      <c r="O41" s="3">
+      <c r="Q41" s="3">
         <v>2700000</v>
       </c>
-      <c r="P41" s="3">
+      <c r="R41" s="3">
         <v>2088400</v>
       </c>
-      <c r="Q41" s="3">
+      <c r="S41" s="3">
         <v>2638000</v>
       </c>
-      <c r="R41" s="3">
+      <c r="T41" s="3">
         <v>2377800</v>
       </c>
-      <c r="S41" s="3">
+      <c r="U41" s="3">
         <v>2801600</v>
       </c>
-      <c r="T41" s="3">
+      <c r="V41" s="3">
         <v>2846400</v>
       </c>
-      <c r="U41" s="3">
+      <c r="W41" s="3">
         <v>1664000</v>
       </c>
-      <c r="V41" s="3">
+      <c r="X41" s="3">
         <v>1630800</v>
       </c>
-      <c r="W41" s="3">
+      <c r="Y41" s="3">
         <v>1856400</v>
       </c>
-      <c r="X41" s="3">
+      <c r="Z41" s="3">
         <v>2157200</v>
       </c>
-      <c r="Y41" s="3">
+      <c r="AA41" s="3">
         <v>2145400</v>
       </c>
-      <c r="Z41" s="3">
+      <c r="AB41" s="3">
         <v>1691900</v>
       </c>
-      <c r="AA41" s="3">
+      <c r="AC41" s="3">
         <v>1687300</v>
       </c>
-      <c r="AB41" s="3">
+      <c r="AD41" s="3">
         <v>1612300</v>
       </c>
-      <c r="AC41" s="3">
+      <c r="AE41" s="3">
         <v>1707400</v>
       </c>
-      <c r="AD41" s="3">
+      <c r="AF41" s="3">
         <v>657300</v>
       </c>
-      <c r="AE41" s="3">
+      <c r="AG41" s="3">
         <v>2559400</v>
       </c>
     </row>
-    <row r="42" spans="2:31" x14ac:dyDescent="0.2">
+    <row r="42" spans="2:33" x14ac:dyDescent="0.2">
       <c r="C42" s="1" t="s">
         <v>35</v>
       </c>
       <c r="D42" s="3">
+        <v>709100</v>
+      </c>
+      <c r="E42" s="3">
+        <v>709100</v>
+      </c>
+      <c r="F42" s="3">
         <v>1411400</v>
       </c>
-      <c r="E42" s="3">
+      <c r="G42" s="3">
         <v>1411400</v>
       </c>
-      <c r="F42" s="3">
+      <c r="H42" s="3">
         <v>634900</v>
       </c>
-      <c r="G42" s="3">
+      <c r="I42" s="3">
         <v>634900</v>
       </c>
-      <c r="H42" s="3">
+      <c r="J42" s="3">
         <v>1058700</v>
       </c>
-      <c r="I42" s="3">
+      <c r="K42" s="3">
         <v>1058700</v>
       </c>
-      <c r="J42" s="3">
+      <c r="L42" s="3">
         <v>639400</v>
       </c>
-      <c r="K42" s="3">
+      <c r="M42" s="3">
         <v>639400</v>
       </c>
-      <c r="L42" s="3">
+      <c r="N42" s="3">
         <v>1024300</v>
       </c>
-      <c r="M42" s="3">
+      <c r="O42" s="3">
         <v>1024300</v>
       </c>
-      <c r="N42" s="3">
+      <c r="P42" s="3">
         <v>306200</v>
       </c>
-      <c r="O42" s="3">
+      <c r="Q42" s="3">
         <v>306200</v>
       </c>
-      <c r="P42" s="3">
+      <c r="R42" s="3">
         <v>596300</v>
       </c>
-      <c r="Q42" s="3">
+      <c r="S42" s="3">
         <v>107600</v>
       </c>
-      <c r="R42" s="3">
+      <c r="T42" s="3">
         <v>3300</v>
       </c>
-      <c r="S42" s="3">
+      <c r="U42" s="3">
         <v>366600</v>
       </c>
-      <c r="T42" s="3">
+      <c r="V42" s="3">
         <v>9900</v>
       </c>
-      <c r="U42" s="3">
+      <c r="W42" s="3">
         <v>193200</v>
       </c>
-      <c r="V42" s="3">
+      <c r="X42" s="3">
         <v>289600</v>
       </c>
-      <c r="W42" s="3">
+      <c r="Y42" s="3">
         <v>78500</v>
       </c>
-      <c r="X42" s="3">
+      <c r="Z42" s="3">
         <v>60200</v>
       </c>
-      <c r="Y42" s="3">
+      <c r="AA42" s="3">
         <v>57200</v>
       </c>
-      <c r="Z42" s="3">
+      <c r="AB42" s="3">
         <v>39900</v>
       </c>
-      <c r="AA42" s="3">
+      <c r="AC42" s="3">
         <v>100100</v>
       </c>
-      <c r="AB42" s="3">
+      <c r="AD42" s="3">
         <v>124800</v>
       </c>
-      <c r="AC42" s="3">
+      <c r="AE42" s="3">
         <v>105100</v>
       </c>
-      <c r="AD42" s="3">
+      <c r="AF42" s="3">
         <v>1667800</v>
       </c>
-      <c r="AE42" s="3">
+      <c r="AG42" s="3">
         <v>174100</v>
       </c>
     </row>
-    <row r="43" spans="2:31" x14ac:dyDescent="0.2">
+    <row r="43" spans="2:33" x14ac:dyDescent="0.2">
       <c r="C43" s="1" t="s">
         <v>36</v>
       </c>
       <c r="D43" s="3">
+        <v>1513500</v>
+      </c>
+      <c r="E43" s="3">
+        <v>1513500</v>
+      </c>
+      <c r="F43" s="3">
         <v>1427900</v>
       </c>
-      <c r="E43" s="3">
+      <c r="G43" s="3">
         <v>1427900</v>
       </c>
-      <c r="F43" s="3">
+      <c r="H43" s="3">
         <v>1486100</v>
       </c>
-      <c r="G43" s="3">
+      <c r="I43" s="3">
         <v>1486100</v>
       </c>
-      <c r="H43" s="3">
+      <c r="J43" s="3">
         <v>1302000</v>
       </c>
-      <c r="I43" s="3">
+      <c r="K43" s="3">
         <v>1302000</v>
       </c>
-      <c r="J43" s="3">
+      <c r="L43" s="3">
         <v>1348000</v>
       </c>
-      <c r="K43" s="3">
+      <c r="M43" s="3">
         <v>1348000</v>
       </c>
-      <c r="L43" s="3">
+      <c r="N43" s="3">
         <v>1208300</v>
       </c>
-      <c r="M43" s="3">
+      <c r="O43" s="3">
         <v>1208300</v>
       </c>
-      <c r="N43" s="3">
+      <c r="P43" s="3">
         <v>1430700</v>
       </c>
-      <c r="O43" s="3">
+      <c r="Q43" s="3">
         <v>1430700</v>
       </c>
-      <c r="P43" s="3">
+      <c r="R43" s="3">
         <v>1189500</v>
       </c>
-      <c r="Q43" s="3">
+      <c r="S43" s="3">
         <v>1296500</v>
       </c>
-      <c r="R43" s="3">
+      <c r="T43" s="3">
         <v>1073900</v>
       </c>
-      <c r="S43" s="3">
+      <c r="U43" s="3">
         <v>1142000</v>
       </c>
-      <c r="T43" s="3">
+      <c r="V43" s="3">
         <v>1070700</v>
       </c>
-      <c r="U43" s="3">
+      <c r="W43" s="3">
         <v>1140000</v>
       </c>
-      <c r="V43" s="3">
+      <c r="X43" s="3">
         <v>1133900</v>
       </c>
-      <c r="W43" s="3">
+      <c r="Y43" s="3">
         <v>1245100</v>
       </c>
-      <c r="X43" s="3">
+      <c r="Z43" s="3">
         <v>1084400</v>
       </c>
-      <c r="Y43" s="3">
+      <c r="AA43" s="3">
         <v>1163800</v>
       </c>
-      <c r="Z43" s="3">
+      <c r="AB43" s="3">
         <v>826300</v>
       </c>
-      <c r="AA43" s="3">
+      <c r="AC43" s="3">
         <v>994200</v>
       </c>
-      <c r="AB43" s="3">
+      <c r="AD43" s="3">
         <v>758500</v>
       </c>
-      <c r="AC43" s="3">
+      <c r="AE43" s="3">
         <v>861800</v>
       </c>
-      <c r="AD43" s="3">
+      <c r="AF43" s="3">
         <v>661200</v>
       </c>
-      <c r="AE43" s="3">
+      <c r="AG43" s="3">
         <v>888900</v>
       </c>
     </row>
-    <row r="44" spans="2:31" x14ac:dyDescent="0.2">
+    <row r="44" spans="2:33" x14ac:dyDescent="0.2">
       <c r="C44" s="1" t="s">
         <v>37</v>
       </c>
       <c r="D44" s="3">
+        <v>1396000</v>
+      </c>
+      <c r="E44" s="3">
+        <v>1396000</v>
+      </c>
+      <c r="F44" s="3">
         <v>1346200</v>
       </c>
-      <c r="E44" s="3">
+      <c r="G44" s="3">
         <v>1346200</v>
       </c>
-      <c r="F44" s="3">
+      <c r="H44" s="3">
         <v>1424300</v>
       </c>
-      <c r="G44" s="3">
+      <c r="I44" s="3">
         <v>1424300</v>
       </c>
-      <c r="H44" s="3">
+      <c r="J44" s="3">
         <v>1319100</v>
       </c>
-      <c r="I44" s="3">
+      <c r="K44" s="3">
         <v>1319100</v>
       </c>
-      <c r="J44" s="3">
+      <c r="L44" s="3">
         <v>1126900</v>
       </c>
-      <c r="K44" s="3">
+      <c r="M44" s="3">
         <v>1126900</v>
       </c>
-      <c r="L44" s="3">
+      <c r="N44" s="3">
         <v>1087700</v>
       </c>
-      <c r="M44" s="3">
+      <c r="O44" s="3">
         <v>1087700</v>
       </c>
-      <c r="N44" s="3">
+      <c r="P44" s="3">
         <v>1266900</v>
       </c>
-      <c r="O44" s="3">
+      <c r="Q44" s="3">
         <v>1266900</v>
       </c>
-      <c r="P44" s="3">
+      <c r="R44" s="3">
         <v>1136800</v>
       </c>
-      <c r="Q44" s="3">
+      <c r="S44" s="3">
         <v>930600</v>
       </c>
-      <c r="R44" s="3">
+      <c r="T44" s="3">
         <v>835600</v>
       </c>
-      <c r="S44" s="3">
+      <c r="U44" s="3">
         <v>839300</v>
       </c>
-      <c r="T44" s="3">
+      <c r="V44" s="3">
         <v>799000</v>
       </c>
-      <c r="U44" s="3">
+      <c r="W44" s="3">
         <v>966400</v>
       </c>
-      <c r="V44" s="3">
+      <c r="X44" s="3">
         <v>942000</v>
       </c>
-      <c r="W44" s="3">
+      <c r="Y44" s="3">
         <v>828200</v>
       </c>
-      <c r="X44" s="3">
+      <c r="Z44" s="3">
         <v>874300</v>
       </c>
-      <c r="Y44" s="3">
+      <c r="AA44" s="3">
         <v>806900</v>
       </c>
-      <c r="Z44" s="3">
+      <c r="AB44" s="3">
         <v>750000</v>
       </c>
-      <c r="AA44" s="3">
+      <c r="AC44" s="3">
         <v>703900</v>
       </c>
-      <c r="AB44" s="3">
+      <c r="AD44" s="3">
         <v>1275900</v>
       </c>
-      <c r="AC44" s="3">
+      <c r="AE44" s="3">
         <v>814600</v>
       </c>
-      <c r="AD44" s="3">
+      <c r="AF44" s="3">
         <v>717200</v>
       </c>
-      <c r="AE44" s="3">
+      <c r="AG44" s="3">
         <v>845500</v>
       </c>
     </row>
-    <row r="45" spans="2:31" x14ac:dyDescent="0.2">
+    <row r="45" spans="2:33" x14ac:dyDescent="0.2">
       <c r="C45" s="1" t="s">
         <v>38</v>
       </c>
       <c r="D45" s="3">
+        <v>67100</v>
+      </c>
+      <c r="E45" s="3">
+        <v>67100</v>
+      </c>
+      <c r="F45" s="3">
         <v>61700</v>
       </c>
-      <c r="E45" s="3">
+      <c r="G45" s="3">
         <v>61700</v>
       </c>
-      <c r="F45" s="3">
+      <c r="H45" s="3">
         <v>78600</v>
       </c>
-      <c r="G45" s="3">
+      <c r="I45" s="3">
         <v>78600</v>
       </c>
-      <c r="H45" s="3">
+      <c r="J45" s="3">
         <v>85600</v>
       </c>
-      <c r="I45" s="3">
+      <c r="K45" s="3">
         <v>85600</v>
       </c>
-      <c r="J45" s="3">
+      <c r="L45" s="3">
         <v>79400</v>
       </c>
-      <c r="K45" s="3">
+      <c r="M45" s="3">
         <v>79400</v>
       </c>
-      <c r="L45" s="3">
+      <c r="N45" s="3">
         <v>72600</v>
       </c>
-      <c r="M45" s="3">
+      <c r="O45" s="3">
         <v>72600</v>
       </c>
-      <c r="N45" s="3">
+      <c r="P45" s="3">
         <v>48900</v>
       </c>
-      <c r="O45" s="3">
+      <c r="Q45" s="3">
         <v>48900</v>
       </c>
-      <c r="P45" s="3">
+      <c r="R45" s="3">
         <v>65000</v>
       </c>
-      <c r="Q45" s="3">
+      <c r="S45" s="3">
         <v>83400</v>
       </c>
-      <c r="R45" s="3">
+      <c r="T45" s="3">
         <v>1687900</v>
       </c>
-      <c r="S45" s="3">
+      <c r="U45" s="3">
         <v>270000</v>
       </c>
-      <c r="T45" s="3">
+      <c r="V45" s="3">
         <v>296600</v>
       </c>
-      <c r="U45" s="3">
+      <c r="W45" s="3">
         <v>560500</v>
       </c>
-      <c r="V45" s="3">
+      <c r="X45" s="3">
         <v>264200</v>
       </c>
-      <c r="W45" s="3">
+      <c r="Y45" s="3">
         <v>122200</v>
       </c>
-      <c r="X45" s="3">
+      <c r="Z45" s="3">
         <v>120900</v>
       </c>
-      <c r="Y45" s="3">
+      <c r="AA45" s="3">
         <v>97600</v>
       </c>
-      <c r="Z45" s="3">
+      <c r="AB45" s="3">
         <v>60600</v>
       </c>
-      <c r="AA45" s="3">
+      <c r="AC45" s="3">
         <v>1025300</v>
       </c>
-      <c r="AB45" s="3">
+      <c r="AD45" s="3">
         <v>1116300</v>
       </c>
-      <c r="AC45" s="3">
+      <c r="AE45" s="3">
         <v>1099200</v>
       </c>
-      <c r="AD45" s="3">
+      <c r="AF45" s="3">
         <v>1035600</v>
       </c>
-      <c r="AE45" s="3">
+      <c r="AG45" s="3">
         <v>54100</v>
       </c>
     </row>
-    <row r="46" spans="2:31" x14ac:dyDescent="0.2">
+    <row r="46" spans="2:33" x14ac:dyDescent="0.2">
       <c r="C46" s="1" t="s">
         <v>39</v>
       </c>
       <c r="D46" s="3">
+        <v>8132400</v>
+      </c>
+      <c r="E46" s="3">
+        <v>8132400</v>
+      </c>
+      <c r="F46" s="3">
         <v>7698500</v>
       </c>
-      <c r="E46" s="3">
+      <c r="G46" s="3">
         <v>7698500</v>
       </c>
-      <c r="F46" s="3">
+      <c r="H46" s="3">
         <v>7248700</v>
       </c>
-      <c r="G46" s="3">
+      <c r="I46" s="3">
         <v>7248700</v>
       </c>
-      <c r="H46" s="3">
+      <c r="J46" s="3">
         <v>6736000</v>
       </c>
-      <c r="I46" s="3">
+      <c r="K46" s="3">
         <v>6736000</v>
       </c>
-      <c r="J46" s="3">
+      <c r="L46" s="3">
         <v>6331900</v>
       </c>
-      <c r="K46" s="3">
+      <c r="M46" s="3">
         <v>6331900</v>
       </c>
-      <c r="L46" s="3">
+      <c r="N46" s="3">
         <v>6058000</v>
       </c>
-      <c r="M46" s="3">
+      <c r="O46" s="3">
         <v>6058000</v>
       </c>
-      <c r="N46" s="3">
+      <c r="P46" s="3">
         <v>5846400</v>
       </c>
-      <c r="O46" s="3">
+      <c r="Q46" s="3">
         <v>5846400</v>
       </c>
-      <c r="P46" s="3">
+      <c r="R46" s="3">
         <v>5184500</v>
       </c>
-      <c r="Q46" s="3">
+      <c r="S46" s="3">
         <v>5056100</v>
       </c>
-      <c r="R46" s="3">
+      <c r="T46" s="3">
         <v>5978500</v>
       </c>
-      <c r="S46" s="3">
+      <c r="U46" s="3">
         <v>5419500</v>
       </c>
-      <c r="T46" s="3">
+      <c r="V46" s="3">
         <v>5022600</v>
       </c>
-      <c r="U46" s="3">
+      <c r="W46" s="3">
         <v>4524100</v>
       </c>
-      <c r="V46" s="3">
+      <c r="X46" s="3">
         <v>4260500</v>
       </c>
-      <c r="W46" s="3">
+      <c r="Y46" s="3">
         <v>4130400</v>
       </c>
-      <c r="X46" s="3">
+      <c r="Z46" s="3">
         <v>4297000</v>
       </c>
-      <c r="Y46" s="3">
+      <c r="AA46" s="3">
         <v>4270900</v>
       </c>
-      <c r="Z46" s="3">
+      <c r="AB46" s="3">
         <v>3368700</v>
       </c>
-      <c r="AA46" s="3">
+      <c r="AC46" s="3">
         <v>4510800</v>
       </c>
-      <c r="AB46" s="3">
+      <c r="AD46" s="3">
         <v>4254800</v>
       </c>
-      <c r="AC46" s="3">
+      <c r="AE46" s="3">
         <v>4588100</v>
       </c>
-      <c r="AD46" s="3">
+      <c r="AF46" s="3">
         <v>4739100</v>
       </c>
-      <c r="AE46" s="3">
+      <c r="AG46" s="3">
         <v>4522000</v>
       </c>
     </row>
-    <row r="47" spans="2:31" x14ac:dyDescent="0.2">
+    <row r="47" spans="2:33" x14ac:dyDescent="0.2">
       <c r="C47" s="1" t="s">
         <v>40</v>
       </c>
       <c r="D47" s="3">
+        <v>6139800</v>
+      </c>
+      <c r="E47" s="3">
+        <v>6139800</v>
+      </c>
+      <c r="F47" s="3">
         <v>6521500</v>
       </c>
-      <c r="E47" s="3">
+      <c r="G47" s="3">
         <v>6521500</v>
       </c>
-      <c r="F47" s="3">
+      <c r="H47" s="3">
         <v>6372200</v>
       </c>
-      <c r="G47" s="3">
+      <c r="I47" s="3">
         <v>6372200</v>
       </c>
-      <c r="H47" s="3">
+      <c r="J47" s="3">
         <v>6369100</v>
       </c>
-      <c r="I47" s="3">
+      <c r="K47" s="3">
         <v>6369100</v>
       </c>
-      <c r="J47" s="3">
+      <c r="L47" s="3">
         <v>5642400</v>
       </c>
-      <c r="K47" s="3">
+      <c r="M47" s="3">
         <v>5642400</v>
       </c>
-      <c r="L47" s="3">
+      <c r="N47" s="3">
         <v>5849000</v>
       </c>
-      <c r="M47" s="3">
+      <c r="O47" s="3">
         <v>5849000</v>
       </c>
-      <c r="N47" s="3">
+      <c r="P47" s="3">
         <v>6021800</v>
       </c>
-      <c r="O47" s="3">
+      <c r="Q47" s="3">
         <v>6021800</v>
       </c>
-      <c r="P47" s="3">
+      <c r="R47" s="3">
         <v>5843200</v>
       </c>
-      <c r="Q47" s="3">
+      <c r="S47" s="3">
         <v>5869300</v>
       </c>
-      <c r="R47" s="3">
+      <c r="T47" s="3">
         <v>5804300</v>
       </c>
-      <c r="S47" s="3">
+      <c r="U47" s="3">
         <v>5263000</v>
       </c>
-      <c r="T47" s="3">
+      <c r="V47" s="3">
         <v>5211000</v>
       </c>
-      <c r="U47" s="3">
+      <c r="W47" s="3">
         <v>4890500</v>
       </c>
-      <c r="V47" s="3">
+      <c r="X47" s="3">
         <v>5212900</v>
       </c>
-      <c r="W47" s="3">
+      <c r="Y47" s="3">
         <v>5251700</v>
       </c>
-      <c r="X47" s="3">
+      <c r="Z47" s="3">
         <v>5383800</v>
       </c>
-      <c r="Y47" s="3">
+      <c r="AA47" s="3">
         <v>5001600</v>
       </c>
-      <c r="Z47" s="3">
+      <c r="AB47" s="3">
         <v>5064000</v>
       </c>
-      <c r="AA47" s="3">
+      <c r="AC47" s="3">
         <v>5144300</v>
       </c>
-      <c r="AB47" s="3">
+      <c r="AD47" s="3">
         <v>4413400</v>
       </c>
-      <c r="AC47" s="3">
+      <c r="AE47" s="3">
         <v>4696600</v>
       </c>
-      <c r="AD47" s="3">
+      <c r="AF47" s="3">
         <v>3860400</v>
       </c>
-      <c r="AE47" s="3">
+      <c r="AG47" s="3">
         <v>3912000</v>
       </c>
     </row>
-    <row r="48" spans="2:31" x14ac:dyDescent="0.2">
+    <row r="48" spans="2:33" x14ac:dyDescent="0.2">
       <c r="C48" s="1" t="s">
         <v>41</v>
       </c>
       <c r="D48" s="3">
+        <v>3783900</v>
+      </c>
+      <c r="E48" s="3">
+        <v>3783900</v>
+      </c>
+      <c r="F48" s="3">
         <v>3814100</v>
       </c>
-      <c r="E48" s="3">
+      <c r="G48" s="3">
         <v>3814100</v>
       </c>
-      <c r="F48" s="3">
+      <c r="H48" s="3">
         <v>3746600</v>
       </c>
-      <c r="G48" s="3">
+      <c r="I48" s="3">
         <v>3746600</v>
       </c>
-      <c r="H48" s="3">
+      <c r="J48" s="3">
         <v>3634800</v>
       </c>
-      <c r="I48" s="3">
+      <c r="K48" s="3">
         <v>3634800</v>
       </c>
-      <c r="J48" s="3">
+      <c r="L48" s="3">
         <v>3522900</v>
       </c>
-      <c r="K48" s="3">
+      <c r="M48" s="3">
         <v>3522900</v>
       </c>
-      <c r="L48" s="3">
+      <c r="N48" s="3">
         <v>3751200</v>
       </c>
-      <c r="M48" s="3">
+      <c r="O48" s="3">
         <v>3751200</v>
       </c>
-      <c r="N48" s="3">
+      <c r="P48" s="3">
         <v>3862400</v>
       </c>
-      <c r="O48" s="3">
+      <c r="Q48" s="3">
         <v>3862400</v>
       </c>
-      <c r="P48" s="3">
+      <c r="R48" s="3">
         <v>3779100</v>
       </c>
-      <c r="Q48" s="3">
+      <c r="S48" s="3">
         <v>4017400</v>
       </c>
-      <c r="R48" s="3">
+      <c r="T48" s="3">
         <v>4069600</v>
       </c>
-      <c r="S48" s="3">
+      <c r="U48" s="3">
         <v>4898400</v>
       </c>
-      <c r="T48" s="3">
+      <c r="V48" s="3">
         <v>4974700</v>
       </c>
-      <c r="U48" s="3">
+      <c r="W48" s="3">
         <v>5430900</v>
       </c>
-      <c r="V48" s="3">
+      <c r="X48" s="3">
         <v>5189600</v>
       </c>
-      <c r="W48" s="3">
+      <c r="Y48" s="3">
         <v>5158600</v>
       </c>
-      <c r="X48" s="3">
+      <c r="Z48" s="3">
         <v>5354300</v>
       </c>
-      <c r="Y48" s="3">
+      <c r="AA48" s="3">
         <v>5098600</v>
       </c>
-      <c r="Z48" s="3">
+      <c r="AB48" s="3">
         <v>3904300</v>
       </c>
-      <c r="AA48" s="3">
+      <c r="AC48" s="3">
         <v>4053300</v>
       </c>
-      <c r="AB48" s="3">
+      <c r="AD48" s="3">
         <v>3815100</v>
       </c>
-      <c r="AC48" s="3">
+      <c r="AE48" s="3">
         <v>4208100</v>
       </c>
-      <c r="AD48" s="3">
+      <c r="AF48" s="3">
         <v>3942500</v>
       </c>
-      <c r="AE48" s="3">
+      <c r="AG48" s="3">
         <v>4338900</v>
       </c>
     </row>
-    <row r="49" spans="3:31" x14ac:dyDescent="0.2">
+    <row r="49" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C49" s="1" t="s">
         <v>42</v>
       </c>
       <c r="D49" s="3">
+        <v>11354500</v>
+      </c>
+      <c r="E49" s="3">
+        <v>11354500</v>
+      </c>
+      <c r="F49" s="3">
         <v>11635100</v>
       </c>
-      <c r="E49" s="3">
+      <c r="G49" s="3">
         <v>11635100</v>
       </c>
-      <c r="F49" s="3">
+      <c r="H49" s="3">
         <v>11668400</v>
       </c>
-      <c r="G49" s="3">
+      <c r="I49" s="3">
         <v>11668400</v>
       </c>
-      <c r="H49" s="3">
+      <c r="J49" s="3">
         <v>11049700</v>
       </c>
-      <c r="I49" s="3">
+      <c r="K49" s="3">
         <v>11049700</v>
       </c>
-      <c r="J49" s="3">
+      <c r="L49" s="3">
         <v>10539400</v>
       </c>
-      <c r="K49" s="3">
+      <c r="M49" s="3">
         <v>10539400</v>
       </c>
-      <c r="L49" s="3">
+      <c r="N49" s="3">
         <v>10807000</v>
       </c>
-      <c r="M49" s="3">
+      <c r="O49" s="3">
         <v>10807000</v>
       </c>
-      <c r="N49" s="3">
+      <c r="P49" s="3">
         <v>10472000</v>
       </c>
-      <c r="O49" s="3">
+      <c r="Q49" s="3">
         <v>10472000</v>
       </c>
-      <c r="P49" s="3">
+      <c r="R49" s="3">
         <v>9926800</v>
       </c>
-      <c r="Q49" s="3">
+      <c r="S49" s="3">
         <v>10372800</v>
       </c>
-      <c r="R49" s="3">
+      <c r="T49" s="3">
         <v>10293600</v>
       </c>
-      <c r="S49" s="3">
+      <c r="U49" s="3">
         <v>6131800</v>
       </c>
-      <c r="T49" s="3">
+      <c r="V49" s="3">
         <v>5697900</v>
       </c>
-      <c r="U49" s="3">
+      <c r="W49" s="3">
         <v>5759700</v>
       </c>
-      <c r="V49" s="3">
+      <c r="X49" s="3">
         <v>5294000</v>
       </c>
-      <c r="W49" s="3">
+      <c r="Y49" s="3">
         <v>4691300</v>
       </c>
-      <c r="X49" s="3">
+      <c r="Z49" s="3">
         <v>4754500</v>
       </c>
-      <c r="Y49" s="3">
+      <c r="AA49" s="3">
         <v>4938500</v>
       </c>
-      <c r="Z49" s="3">
+      <c r="AB49" s="3">
         <v>4335000</v>
       </c>
-      <c r="AA49" s="3">
+      <c r="AC49" s="3">
         <v>4369000</v>
       </c>
-      <c r="AB49" s="3">
+      <c r="AD49" s="3">
         <v>4175000</v>
       </c>
-      <c r="AC49" s="3">
+      <c r="AE49" s="3">
         <v>3613600</v>
       </c>
-      <c r="AD49" s="3">
+      <c r="AF49" s="3">
         <v>3569400</v>
       </c>
-      <c r="AE49" s="3">
+      <c r="AG49" s="3">
         <v>3614300</v>
       </c>
     </row>
-    <row r="50" spans="3:31" x14ac:dyDescent="0.2">
+    <row r="50" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C50" s="1" t="s">
         <v>43</v>
       </c>
@@ -4159,8 +4387,14 @@
       <c r="AE50" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="51" spans="3:31" x14ac:dyDescent="0.2">
+      <c r="AF50" s="3">
+        <v>0</v>
+      </c>
+      <c r="AG50" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="51" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C51" s="1" t="s">
         <v>44</v>
       </c>
@@ -4248,97 +4482,109 @@
       <c r="AE51" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="52" spans="3:31" x14ac:dyDescent="0.2">
+      <c r="AF51" s="3">
+        <v>0</v>
+      </c>
+      <c r="AG51" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="52" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C52" s="1" t="s">
         <v>45</v>
       </c>
       <c r="D52" s="3">
+        <v>884300</v>
+      </c>
+      <c r="E52" s="3">
+        <v>884300</v>
+      </c>
+      <c r="F52" s="3">
         <v>789200</v>
       </c>
-      <c r="E52" s="3">
+      <c r="G52" s="3">
         <v>789200</v>
       </c>
-      <c r="F52" s="3">
+      <c r="H52" s="3">
         <v>752100</v>
       </c>
-      <c r="G52" s="3">
+      <c r="I52" s="3">
         <v>752100</v>
       </c>
-      <c r="H52" s="3">
+      <c r="J52" s="3">
         <v>702300</v>
       </c>
-      <c r="I52" s="3">
+      <c r="K52" s="3">
         <v>702300</v>
       </c>
-      <c r="J52" s="3">
+      <c r="L52" s="3">
         <v>765600</v>
       </c>
-      <c r="K52" s="3">
+      <c r="M52" s="3">
         <v>765600</v>
       </c>
-      <c r="L52" s="3">
+      <c r="N52" s="3">
         <v>660900</v>
       </c>
-      <c r="M52" s="3">
+      <c r="O52" s="3">
         <v>660900</v>
       </c>
-      <c r="N52" s="3">
+      <c r="P52" s="3">
         <v>680800</v>
       </c>
-      <c r="O52" s="3">
+      <c r="Q52" s="3">
         <v>680800</v>
       </c>
-      <c r="P52" s="3">
+      <c r="R52" s="3">
         <v>545700</v>
       </c>
-      <c r="Q52" s="3">
+      <c r="S52" s="3">
         <v>744100</v>
       </c>
-      <c r="R52" s="3">
+      <c r="T52" s="3">
         <v>797600</v>
       </c>
-      <c r="S52" s="3">
+      <c r="U52" s="3">
         <v>835900</v>
       </c>
-      <c r="T52" s="3">
+      <c r="V52" s="3">
         <v>976300</v>
       </c>
-      <c r="U52" s="3">
+      <c r="W52" s="3">
         <v>977200</v>
       </c>
-      <c r="V52" s="3">
+      <c r="X52" s="3">
         <v>944500</v>
       </c>
-      <c r="W52" s="3">
+      <c r="Y52" s="3">
         <v>645900</v>
       </c>
-      <c r="X52" s="3">
+      <c r="Z52" s="3">
         <v>664900</v>
       </c>
-      <c r="Y52" s="3">
+      <c r="AA52" s="3">
         <v>687200</v>
       </c>
-      <c r="Z52" s="3">
+      <c r="AB52" s="3">
         <v>543400</v>
       </c>
-      <c r="AA52" s="3">
+      <c r="AC52" s="3">
         <v>535400</v>
       </c>
-      <c r="AB52" s="3">
+      <c r="AD52" s="3">
         <v>540700</v>
       </c>
-      <c r="AC52" s="3">
+      <c r="AE52" s="3">
         <v>585000</v>
       </c>
-      <c r="AD52" s="3">
+      <c r="AF52" s="3">
         <v>530600</v>
       </c>
-      <c r="AE52" s="3">
+      <c r="AG52" s="3">
         <v>601800</v>
       </c>
     </row>
-    <row r="53" spans="3:31" x14ac:dyDescent="0.2">
+    <row r="53" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C53" s="1" t="s">
         <v>46</v>
       </c>
@@ -4426,97 +4672,109 @@
       <c r="AE53" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="54" spans="3:31" x14ac:dyDescent="0.2">
+      <c r="AF53" s="3">
+        <v>0</v>
+      </c>
+      <c r="AG53" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="54" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C54" s="1" t="s">
         <v>47</v>
       </c>
       <c r="D54" s="3">
+        <v>30580500</v>
+      </c>
+      <c r="E54" s="3">
+        <v>30580500</v>
+      </c>
+      <c r="F54" s="3">
         <v>30647600</v>
       </c>
-      <c r="E54" s="3">
+      <c r="G54" s="3">
         <v>30647600</v>
       </c>
-      <c r="F54" s="3">
+      <c r="H54" s="3">
         <v>29981000</v>
       </c>
-      <c r="G54" s="3">
+      <c r="I54" s="3">
         <v>29981000</v>
       </c>
-      <c r="H54" s="3">
+      <c r="J54" s="3">
         <v>28677900</v>
       </c>
-      <c r="I54" s="3">
+      <c r="K54" s="3">
         <v>28677900</v>
       </c>
-      <c r="J54" s="3">
+      <c r="L54" s="3">
         <v>27001300</v>
       </c>
-      <c r="K54" s="3">
+      <c r="M54" s="3">
         <v>27001300</v>
       </c>
-      <c r="L54" s="3">
+      <c r="N54" s="3">
         <v>27357500</v>
       </c>
-      <c r="M54" s="3">
+      <c r="O54" s="3">
         <v>27357500</v>
       </c>
-      <c r="N54" s="3">
+      <c r="P54" s="3">
         <v>27087700</v>
       </c>
-      <c r="O54" s="3">
+      <c r="Q54" s="3">
         <v>27087700</v>
       </c>
-      <c r="P54" s="3">
+      <c r="R54" s="3">
         <v>25491800</v>
       </c>
-      <c r="Q54" s="3">
+      <c r="S54" s="3">
         <v>26059700</v>
       </c>
-      <c r="R54" s="3">
+      <c r="T54" s="3">
         <v>26943600</v>
       </c>
-      <c r="S54" s="3">
+      <c r="U54" s="3">
         <v>22548600</v>
       </c>
-      <c r="T54" s="3">
+      <c r="V54" s="3">
         <v>21882500</v>
       </c>
-      <c r="U54" s="3">
+      <c r="W54" s="3">
         <v>21582400</v>
       </c>
-      <c r="V54" s="3">
+      <c r="X54" s="3">
         <v>20901500</v>
       </c>
-      <c r="W54" s="3">
+      <c r="Y54" s="3">
         <v>19877900</v>
       </c>
-      <c r="X54" s="3">
+      <c r="Z54" s="3">
         <v>20454500</v>
       </c>
-      <c r="Y54" s="3">
+      <c r="AA54" s="3">
         <v>19996800</v>
       </c>
-      <c r="Z54" s="3">
+      <c r="AB54" s="3">
         <v>17215400</v>
       </c>
-      <c r="AA54" s="3">
+      <c r="AC54" s="3">
         <v>18612800</v>
       </c>
-      <c r="AB54" s="3">
+      <c r="AD54" s="3">
         <v>17199000</v>
       </c>
-      <c r="AC54" s="3">
+      <c r="AE54" s="3">
         <v>17691400</v>
       </c>
-      <c r="AD54" s="3">
+      <c r="AF54" s="3">
         <v>16642000</v>
       </c>
-      <c r="AE54" s="3">
+      <c r="AG54" s="3">
         <v>16989000</v>
       </c>
     </row>
-    <row r="55" spans="3:31" x14ac:dyDescent="0.2">
+    <row r="55" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C55" s="1" t="s">
         <v>48</v>
       </c>
@@ -4548,8 +4806,10 @@
       <c r="AC55" s="3"/>
       <c r="AD55" s="3"/>
       <c r="AE55" s="3"/>
-    </row>
-    <row r="56" spans="3:31" x14ac:dyDescent="0.2">
+      <c r="AF55" s="3"/>
+      <c r="AG55" s="3"/>
+    </row>
+    <row r="56" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C56" s="1" t="s">
         <v>49</v>
       </c>
@@ -4581,542 +4841,580 @@
       <c r="AC56" s="3"/>
       <c r="AD56" s="3"/>
       <c r="AE56" s="3"/>
-    </row>
-    <row r="57" spans="3:31" x14ac:dyDescent="0.2">
+      <c r="AF56" s="3"/>
+      <c r="AG56" s="3"/>
+    </row>
+    <row r="57" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C57" s="1" t="s">
         <v>50</v>
       </c>
       <c r="D57" s="3">
+        <v>569700</v>
+      </c>
+      <c r="E57" s="3">
+        <v>569700</v>
+      </c>
+      <c r="F57" s="3">
         <v>566200</v>
       </c>
-      <c r="E57" s="3">
+      <c r="G57" s="3">
         <v>566200</v>
       </c>
-      <c r="F57" s="3">
+      <c r="H57" s="3">
         <v>539700</v>
       </c>
-      <c r="G57" s="3">
+      <c r="I57" s="3">
         <v>539700</v>
       </c>
-      <c r="H57" s="3">
+      <c r="J57" s="3">
         <v>561300</v>
       </c>
-      <c r="I57" s="3">
+      <c r="K57" s="3">
         <v>561300</v>
       </c>
-      <c r="J57" s="3">
+      <c r="L57" s="3">
         <v>559200</v>
       </c>
-      <c r="K57" s="3">
+      <c r="M57" s="3">
         <v>559200</v>
       </c>
-      <c r="L57" s="3">
+      <c r="N57" s="3">
         <v>578400</v>
       </c>
-      <c r="M57" s="3">
+      <c r="O57" s="3">
         <v>578400</v>
       </c>
-      <c r="N57" s="3">
+      <c r="P57" s="3">
         <v>620600</v>
       </c>
-      <c r="O57" s="3">
+      <c r="Q57" s="3">
         <v>620600</v>
       </c>
-      <c r="P57" s="3">
+      <c r="R57" s="3">
         <v>585200</v>
       </c>
-      <c r="Q57" s="3">
+      <c r="S57" s="3">
         <v>1722900</v>
       </c>
-      <c r="R57" s="3">
+      <c r="T57" s="3">
         <v>1552800</v>
       </c>
-      <c r="S57" s="3">
+      <c r="U57" s="3">
         <v>1645600</v>
       </c>
-      <c r="T57" s="3">
+      <c r="V57" s="3">
         <v>1569300</v>
       </c>
-      <c r="U57" s="3">
+      <c r="W57" s="3">
         <v>1578100</v>
       </c>
-      <c r="V57" s="3">
+      <c r="X57" s="3">
         <v>1362600</v>
       </c>
-      <c r="W57" s="3">
+      <c r="Y57" s="3">
         <v>1388900</v>
       </c>
-      <c r="X57" s="3">
+      <c r="Z57" s="3">
         <v>1333900</v>
       </c>
-      <c r="Y57" s="3">
+      <c r="AA57" s="3">
         <v>1334900</v>
       </c>
-      <c r="Z57" s="3">
+      <c r="AB57" s="3">
         <v>1064500</v>
       </c>
-      <c r="AA57" s="3">
+      <c r="AC57" s="3">
         <v>1324400</v>
       </c>
-      <c r="AB57" s="3">
+      <c r="AD57" s="3">
         <v>1241000</v>
       </c>
-      <c r="AC57" s="3">
+      <c r="AE57" s="3">
         <v>1131800</v>
       </c>
-      <c r="AD57" s="3">
+      <c r="AF57" s="3">
         <v>409500</v>
       </c>
-      <c r="AE57" s="3">
+      <c r="AG57" s="3">
         <v>1398900</v>
       </c>
     </row>
-    <row r="58" spans="3:31" x14ac:dyDescent="0.2">
+    <row r="58" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C58" s="1" t="s">
         <v>51</v>
       </c>
       <c r="D58" s="3">
-        <v>2526500</v>
+        <v>2367600</v>
       </c>
       <c r="E58" s="3">
-        <v>2526500</v>
+        <v>2367600</v>
       </c>
       <c r="F58" s="3">
+        <v>2550000</v>
+      </c>
+      <c r="G58" s="3">
+        <v>2550000</v>
+      </c>
+      <c r="H58" s="3">
         <v>2760400</v>
       </c>
-      <c r="G58" s="3">
+      <c r="I58" s="3">
         <v>2760400</v>
       </c>
-      <c r="H58" s="3">
+      <c r="J58" s="3">
         <v>2548700</v>
       </c>
-      <c r="I58" s="3">
+      <c r="K58" s="3">
         <v>2548700</v>
       </c>
-      <c r="J58" s="3">
+      <c r="L58" s="3">
         <v>2493700</v>
       </c>
-      <c r="K58" s="3">
+      <c r="M58" s="3">
         <v>2493700</v>
       </c>
-      <c r="L58" s="3">
+      <c r="N58" s="3">
         <v>2195300</v>
       </c>
-      <c r="M58" s="3">
+      <c r="O58" s="3">
         <v>2195300</v>
       </c>
-      <c r="N58" s="3">
+      <c r="P58" s="3">
         <v>2243800</v>
       </c>
-      <c r="O58" s="3">
+      <c r="Q58" s="3">
         <v>2243800</v>
       </c>
-      <c r="P58" s="3">
+      <c r="R58" s="3">
         <v>1824300</v>
       </c>
-      <c r="Q58" s="3">
+      <c r="S58" s="3">
         <v>1955200</v>
       </c>
-      <c r="R58" s="3">
+      <c r="T58" s="3">
         <v>1803200</v>
       </c>
-      <c r="S58" s="3">
+      <c r="U58" s="3">
         <v>3008300</v>
       </c>
-      <c r="T58" s="3">
+      <c r="V58" s="3">
         <v>2262800</v>
       </c>
-      <c r="U58" s="3">
+      <c r="W58" s="3">
         <v>1759500</v>
       </c>
-      <c r="V58" s="3">
+      <c r="X58" s="3">
         <v>2281100</v>
       </c>
-      <c r="W58" s="3">
+      <c r="Y58" s="3">
         <v>1832200</v>
       </c>
-      <c r="X58" s="3">
+      <c r="Z58" s="3">
         <v>1460400</v>
       </c>
-      <c r="Y58" s="3">
+      <c r="AA58" s="3">
         <v>1547100</v>
       </c>
-      <c r="Z58" s="3">
+      <c r="AB58" s="3">
         <v>1280700</v>
       </c>
-      <c r="AA58" s="3">
+      <c r="AC58" s="3">
         <v>1178600</v>
       </c>
-      <c r="AB58" s="3">
+      <c r="AD58" s="3">
         <v>998600</v>
       </c>
-      <c r="AC58" s="3">
+      <c r="AE58" s="3">
         <v>1273300</v>
       </c>
-      <c r="AD58" s="3">
+      <c r="AF58" s="3">
         <v>912000</v>
       </c>
-      <c r="AE58" s="3">
+      <c r="AG58" s="3">
         <v>1169600</v>
       </c>
     </row>
-    <row r="59" spans="3:31" x14ac:dyDescent="0.2">
+    <row r="59" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C59" s="1" t="s">
         <v>52</v>
       </c>
       <c r="D59" s="3">
-        <v>1222900</v>
+        <v>2309900</v>
       </c>
       <c r="E59" s="3">
-        <v>1222900</v>
+        <v>2309900</v>
       </c>
       <c r="F59" s="3">
+        <v>1199400</v>
+      </c>
+      <c r="G59" s="3">
+        <v>1199400</v>
+      </c>
+      <c r="H59" s="3">
         <v>2391300</v>
       </c>
-      <c r="G59" s="3">
+      <c r="I59" s="3">
         <v>2391300</v>
       </c>
-      <c r="H59" s="3">
+      <c r="J59" s="3">
         <v>1005600</v>
       </c>
-      <c r="I59" s="3">
+      <c r="K59" s="3">
         <v>1005600</v>
       </c>
-      <c r="J59" s="3">
+      <c r="L59" s="3">
         <v>1968600</v>
       </c>
-      <c r="K59" s="3">
+      <c r="M59" s="3">
         <v>1968600</v>
       </c>
-      <c r="L59" s="3">
+      <c r="N59" s="3">
         <v>1016800</v>
       </c>
-      <c r="M59" s="3">
+      <c r="O59" s="3">
         <v>1016800</v>
       </c>
-      <c r="N59" s="3">
+      <c r="P59" s="3">
         <v>1979000</v>
       </c>
-      <c r="O59" s="3">
+      <c r="Q59" s="3">
         <v>1979000</v>
       </c>
-      <c r="P59" s="3">
+      <c r="R59" s="3">
         <v>975800</v>
       </c>
-      <c r="Q59" s="3">
+      <c r="S59" s="3">
         <v>1144600</v>
       </c>
-      <c r="R59" s="3">
+      <c r="T59" s="3">
         <v>1474800</v>
       </c>
-      <c r="S59" s="3">
+      <c r="U59" s="3">
         <v>551900</v>
       </c>
-      <c r="T59" s="3">
+      <c r="V59" s="3">
         <v>665200</v>
       </c>
-      <c r="U59" s="3">
+      <c r="W59" s="3">
         <v>513900</v>
       </c>
-      <c r="V59" s="3">
+      <c r="X59" s="3">
         <v>496600</v>
       </c>
-      <c r="W59" s="3">
+      <c r="Y59" s="3">
         <v>479500</v>
       </c>
-      <c r="X59" s="3">
+      <c r="Z59" s="3">
         <v>461700</v>
       </c>
-      <c r="Y59" s="3">
+      <c r="AA59" s="3">
         <v>438300</v>
       </c>
-      <c r="Z59" s="3">
+      <c r="AB59" s="3">
         <v>376600</v>
       </c>
-      <c r="AA59" s="3">
+      <c r="AC59" s="3">
         <v>711700</v>
       </c>
-      <c r="AB59" s="3">
+      <c r="AD59" s="3">
         <v>829000</v>
       </c>
-      <c r="AC59" s="3">
+      <c r="AE59" s="3">
         <v>718100</v>
       </c>
-      <c r="AD59" s="3">
+      <c r="AF59" s="3">
         <v>1491700</v>
       </c>
-      <c r="AE59" s="3">
+      <c r="AG59" s="3">
         <v>321900</v>
       </c>
     </row>
-    <row r="60" spans="3:31" x14ac:dyDescent="0.2">
+    <row r="60" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C60" s="1" t="s">
         <v>53</v>
       </c>
       <c r="D60" s="3">
+        <v>5247200</v>
+      </c>
+      <c r="E60" s="3">
+        <v>5247200</v>
+      </c>
+      <c r="F60" s="3">
         <v>5338300</v>
       </c>
-      <c r="E60" s="3">
+      <c r="G60" s="3">
         <v>5338300</v>
       </c>
-      <c r="F60" s="3">
+      <c r="H60" s="3">
         <v>5691400</v>
       </c>
-      <c r="G60" s="3">
+      <c r="I60" s="3">
         <v>5691400</v>
       </c>
-      <c r="H60" s="3">
+      <c r="J60" s="3">
         <v>4993000</v>
       </c>
-      <c r="I60" s="3">
+      <c r="K60" s="3">
         <v>4993000</v>
       </c>
-      <c r="J60" s="3">
+      <c r="L60" s="3">
         <v>5021500</v>
       </c>
-      <c r="K60" s="3">
+      <c r="M60" s="3">
         <v>5021500</v>
       </c>
-      <c r="L60" s="3">
+      <c r="N60" s="3">
         <v>4592600</v>
       </c>
-      <c r="M60" s="3">
+      <c r="O60" s="3">
         <v>4592600</v>
       </c>
-      <c r="N60" s="3">
+      <c r="P60" s="3">
         <v>4843400</v>
       </c>
-      <c r="O60" s="3">
+      <c r="Q60" s="3">
         <v>4843400</v>
       </c>
-      <c r="P60" s="3">
+      <c r="R60" s="3">
         <v>4108600</v>
       </c>
-      <c r="Q60" s="3">
+      <c r="S60" s="3">
         <v>4822700</v>
       </c>
-      <c r="R60" s="3">
+      <c r="T60" s="3">
         <v>4830800</v>
       </c>
-      <c r="S60" s="3">
+      <c r="U60" s="3">
         <v>5205800</v>
       </c>
-      <c r="T60" s="3">
+      <c r="V60" s="3">
         <v>4497300</v>
       </c>
-      <c r="U60" s="3">
+      <c r="W60" s="3">
         <v>3851500</v>
       </c>
-      <c r="V60" s="3">
+      <c r="X60" s="3">
         <v>4140300</v>
       </c>
-      <c r="W60" s="3">
+      <c r="Y60" s="3">
         <v>3700600</v>
       </c>
-      <c r="X60" s="3">
+      <c r="Z60" s="3">
         <v>3256000</v>
       </c>
-      <c r="Y60" s="3">
+      <c r="AA60" s="3">
         <v>3320300</v>
       </c>
-      <c r="Z60" s="3">
+      <c r="AB60" s="3">
         <v>2721800</v>
       </c>
-      <c r="AA60" s="3">
+      <c r="AC60" s="3">
         <v>3214700</v>
       </c>
-      <c r="AB60" s="3">
+      <c r="AD60" s="3">
         <v>3068600</v>
       </c>
-      <c r="AC60" s="3">
+      <c r="AE60" s="3">
         <v>3123200</v>
       </c>
-      <c r="AD60" s="3">
+      <c r="AF60" s="3">
         <v>2813200</v>
       </c>
-      <c r="AE60" s="3">
+      <c r="AG60" s="3">
         <v>2890400</v>
       </c>
     </row>
-    <row r="61" spans="3:31" x14ac:dyDescent="0.2">
+    <row r="61" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C61" s="1" t="s">
         <v>54</v>
       </c>
       <c r="D61" s="3">
-        <v>10487600</v>
+        <v>10715600</v>
       </c>
       <c r="E61" s="3">
-        <v>10487600</v>
+        <v>10715600</v>
       </c>
       <c r="F61" s="3">
+        <v>10524800</v>
+      </c>
+      <c r="G61" s="3">
+        <v>10524800</v>
+      </c>
+      <c r="H61" s="3">
         <v>10163300</v>
       </c>
-      <c r="G61" s="3">
+      <c r="I61" s="3">
         <v>10163300</v>
       </c>
-      <c r="H61" s="3">
+      <c r="J61" s="3">
         <v>9987600</v>
       </c>
-      <c r="I61" s="3">
+      <c r="K61" s="3">
         <v>9987600</v>
       </c>
-      <c r="J61" s="3">
+      <c r="L61" s="3">
         <v>9134100</v>
       </c>
-      <c r="K61" s="3">
+      <c r="M61" s="3">
         <v>9134100</v>
       </c>
-      <c r="L61" s="3">
+      <c r="N61" s="3">
         <v>9416200</v>
       </c>
-      <c r="M61" s="3">
+      <c r="O61" s="3">
         <v>9416200</v>
       </c>
-      <c r="N61" s="3">
+      <c r="P61" s="3">
         <v>9407700</v>
       </c>
-      <c r="O61" s="3">
+      <c r="Q61" s="3">
         <v>9407700</v>
       </c>
-      <c r="P61" s="3">
+      <c r="R61" s="3">
         <v>9398000</v>
       </c>
-      <c r="Q61" s="3">
+      <c r="S61" s="3">
         <v>8997100</v>
       </c>
-      <c r="R61" s="3">
+      <c r="T61" s="3">
         <v>9135300</v>
       </c>
-      <c r="S61" s="3">
+      <c r="U61" s="3">
         <v>6597300</v>
       </c>
-      <c r="T61" s="3">
+      <c r="V61" s="3">
         <v>6668000</v>
       </c>
-      <c r="U61" s="3">
+      <c r="W61" s="3">
         <v>6870800</v>
       </c>
-      <c r="V61" s="3">
+      <c r="X61" s="3">
         <v>6236800</v>
       </c>
-      <c r="W61" s="3">
+      <c r="Y61" s="3">
         <v>5955800</v>
       </c>
-      <c r="X61" s="3">
+      <c r="Z61" s="3">
         <v>6509300</v>
       </c>
-      <c r="Y61" s="3">
+      <c r="AA61" s="3">
         <v>6063600</v>
       </c>
-      <c r="Z61" s="3">
+      <c r="AB61" s="3">
         <v>4827700</v>
       </c>
-      <c r="AA61" s="3">
+      <c r="AC61" s="3">
         <v>5388500</v>
       </c>
-      <c r="AB61" s="3">
+      <c r="AD61" s="3">
         <v>5363300</v>
       </c>
-      <c r="AC61" s="3">
+      <c r="AE61" s="3">
         <v>5332500</v>
       </c>
-      <c r="AD61" s="3">
+      <c r="AF61" s="3">
         <v>4893900</v>
       </c>
-      <c r="AE61" s="3">
+      <c r="AG61" s="3">
         <v>5017100</v>
       </c>
     </row>
-    <row r="62" spans="3:31" x14ac:dyDescent="0.2">
+    <row r="62" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C62" s="1" t="s">
         <v>55</v>
       </c>
       <c r="D62" s="3">
-        <v>1160300</v>
+        <v>782700</v>
       </c>
       <c r="E62" s="3">
-        <v>1160300</v>
+        <v>782700</v>
       </c>
       <c r="F62" s="3">
+        <v>1123100</v>
+      </c>
+      <c r="G62" s="3">
+        <v>1123100</v>
+      </c>
+      <c r="H62" s="3">
         <v>871000</v>
       </c>
-      <c r="G62" s="3">
+      <c r="I62" s="3">
         <v>871000</v>
       </c>
-      <c r="H62" s="3">
+      <c r="J62" s="3">
         <v>1252300</v>
       </c>
-      <c r="I62" s="3">
+      <c r="K62" s="3">
         <v>1252300</v>
       </c>
-      <c r="J62" s="3">
+      <c r="L62" s="3">
         <v>826200</v>
       </c>
-      <c r="K62" s="3">
+      <c r="M62" s="3">
         <v>826200</v>
       </c>
-      <c r="L62" s="3">
+      <c r="N62" s="3">
         <v>1260100</v>
       </c>
-      <c r="M62" s="3">
+      <c r="O62" s="3">
         <v>1260100</v>
       </c>
-      <c r="N62" s="3">
+      <c r="P62" s="3">
         <v>818400</v>
       </c>
-      <c r="O62" s="3">
+      <c r="Q62" s="3">
         <v>818400</v>
       </c>
-      <c r="P62" s="3">
+      <c r="R62" s="3">
         <v>1216700</v>
       </c>
-      <c r="Q62" s="3">
+      <c r="S62" s="3">
         <v>1803000</v>
       </c>
-      <c r="R62" s="3">
+      <c r="T62" s="3">
         <v>2349000</v>
       </c>
-      <c r="S62" s="3">
+      <c r="U62" s="3">
         <v>1818300</v>
       </c>
-      <c r="T62" s="3">
+      <c r="V62" s="3">
         <v>1959200</v>
       </c>
-      <c r="U62" s="3">
+      <c r="W62" s="3">
         <v>1859300</v>
       </c>
-      <c r="V62" s="3">
+      <c r="X62" s="3">
         <v>1814000</v>
       </c>
-      <c r="W62" s="3">
+      <c r="Y62" s="3">
         <v>1778600</v>
       </c>
-      <c r="X62" s="3">
+      <c r="Z62" s="3">
         <v>1946700</v>
       </c>
-      <c r="Y62" s="3">
+      <c r="AA62" s="3">
         <v>1970500</v>
       </c>
-      <c r="Z62" s="3">
+      <c r="AB62" s="3">
         <v>1631600</v>
       </c>
-      <c r="AA62" s="3">
+      <c r="AC62" s="3">
         <v>1615700</v>
       </c>
-      <c r="AB62" s="3">
+      <c r="AD62" s="3">
         <v>1432700</v>
       </c>
-      <c r="AC62" s="3">
+      <c r="AE62" s="3">
         <v>1345400</v>
       </c>
-      <c r="AD62" s="3">
+      <c r="AF62" s="3">
         <v>1217900</v>
       </c>
-      <c r="AE62" s="3">
+      <c r="AG62" s="3">
         <v>1225400</v>
       </c>
     </row>
-    <row r="63" spans="3:31" x14ac:dyDescent="0.2">
+    <row r="63" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C63" s="1" t="s">
         <v>56</v>
       </c>
@@ -5204,8 +5502,14 @@
       <c r="AE63" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="64" spans="3:31" x14ac:dyDescent="0.2">
+      <c r="AF63" s="3">
+        <v>0</v>
+      </c>
+      <c r="AG63" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="64" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C64" s="1" t="s">
         <v>20</v>
       </c>
@@ -5293,8 +5597,14 @@
       <c r="AE64" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="65" spans="2:31" x14ac:dyDescent="0.2">
+      <c r="AF64" s="3">
+        <v>0</v>
+      </c>
+      <c r="AG64" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="65" spans="2:33" x14ac:dyDescent="0.2">
       <c r="C65" s="1" t="s">
         <v>57</v>
       </c>
@@ -5382,97 +5692,109 @@
       <c r="AE65" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="66" spans="2:31" x14ac:dyDescent="0.2">
+      <c r="AF65" s="3">
+        <v>0</v>
+      </c>
+      <c r="AG65" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="66" spans="2:33" x14ac:dyDescent="0.2">
       <c r="C66" s="1" t="s">
         <v>58</v>
       </c>
       <c r="D66" s="3">
+        <v>17541300</v>
+      </c>
+      <c r="E66" s="3">
+        <v>17541300</v>
+      </c>
+      <c r="F66" s="3">
         <v>17524000</v>
       </c>
-      <c r="E66" s="3">
+      <c r="G66" s="3">
         <v>17524000</v>
       </c>
-      <c r="F66" s="3">
+      <c r="H66" s="3">
         <v>17594700</v>
       </c>
-      <c r="G66" s="3">
+      <c r="I66" s="3">
         <v>17594700</v>
       </c>
-      <c r="H66" s="3">
+      <c r="J66" s="3">
         <v>16747700</v>
       </c>
-      <c r="I66" s="3">
+      <c r="K66" s="3">
         <v>16747700</v>
       </c>
-      <c r="J66" s="3">
+      <c r="L66" s="3">
         <v>15799300</v>
       </c>
-      <c r="K66" s="3">
+      <c r="M66" s="3">
         <v>15799300</v>
       </c>
-      <c r="L66" s="3">
+      <c r="N66" s="3">
         <v>15790600</v>
       </c>
-      <c r="M66" s="3">
+      <c r="O66" s="3">
         <v>15790600</v>
       </c>
-      <c r="N66" s="3">
+      <c r="P66" s="3">
         <v>15878600</v>
       </c>
-      <c r="O66" s="3">
+      <c r="Q66" s="3">
         <v>15878600</v>
       </c>
-      <c r="P66" s="3">
+      <c r="R66" s="3">
         <v>15126000</v>
       </c>
-      <c r="Q66" s="3">
+      <c r="S66" s="3">
         <v>22876100</v>
       </c>
-      <c r="R66" s="3">
+      <c r="T66" s="3">
         <v>23803600</v>
       </c>
-      <c r="S66" s="3">
+      <c r="U66" s="3">
         <v>19583400</v>
       </c>
-      <c r="T66" s="3">
+      <c r="V66" s="3">
         <v>18953800</v>
       </c>
-      <c r="U66" s="3">
+      <c r="W66" s="3">
         <v>18589100</v>
       </c>
-      <c r="V66" s="3">
+      <c r="X66" s="3">
         <v>17817900</v>
       </c>
-      <c r="W66" s="3">
+      <c r="Y66" s="3">
         <v>16772900</v>
       </c>
-      <c r="X66" s="3">
+      <c r="Z66" s="3">
         <v>17227400</v>
       </c>
-      <c r="Y66" s="3">
+      <c r="AA66" s="3">
         <v>16723000</v>
       </c>
-      <c r="Z66" s="3">
+      <c r="AB66" s="3">
         <v>14103400</v>
       </c>
-      <c r="AA66" s="3">
+      <c r="AC66" s="3">
         <v>15275800</v>
       </c>
-      <c r="AB66" s="3">
+      <c r="AD66" s="3">
         <v>14128800</v>
       </c>
-      <c r="AC66" s="3">
+      <c r="AE66" s="3">
         <v>14292500</v>
       </c>
-      <c r="AD66" s="3">
+      <c r="AF66" s="3">
         <v>13213600</v>
       </c>
-      <c r="AE66" s="3">
+      <c r="AG66" s="3">
         <v>13347900</v>
       </c>
     </row>
-    <row r="67" spans="2:31" x14ac:dyDescent="0.2">
+    <row r="67" spans="2:33" x14ac:dyDescent="0.2">
       <c r="C67" s="1" t="s">
         <v>59</v>
       </c>
@@ -5504,8 +5826,10 @@
       <c r="AC67" s="3"/>
       <c r="AD67" s="3"/>
       <c r="AE67" s="3"/>
-    </row>
-    <row r="68" spans="2:31" x14ac:dyDescent="0.2">
+      <c r="AF67" s="3"/>
+      <c r="AG67" s="3"/>
+    </row>
+    <row r="68" spans="2:33" x14ac:dyDescent="0.2">
       <c r="C68" s="1" t="s">
         <v>60</v>
       </c>
@@ -5593,8 +5917,14 @@
       <c r="AE68" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="69" spans="2:31" x14ac:dyDescent="0.2">
+      <c r="AF68" s="3">
+        <v>0</v>
+      </c>
+      <c r="AG68" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="69" spans="2:33" x14ac:dyDescent="0.2">
       <c r="C69" s="1" t="s">
         <v>61</v>
       </c>
@@ -5682,8 +6012,14 @@
       <c r="AE69" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="70" spans="2:31" x14ac:dyDescent="0.2">
+      <c r="AF69" s="3">
+        <v>0</v>
+      </c>
+      <c r="AG69" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="70" spans="2:33" x14ac:dyDescent="0.2">
       <c r="C70" s="1" t="s">
         <v>62</v>
       </c>
@@ -5771,8 +6107,14 @@
       <c r="AE70" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="71" spans="2:31" x14ac:dyDescent="0.2">
+      <c r="AF70" s="3">
+        <v>0</v>
+      </c>
+      <c r="AG70" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="71" spans="2:33" x14ac:dyDescent="0.2">
       <c r="C71" s="1" t="s">
         <v>63</v>
       </c>
@@ -5860,97 +6202,109 @@
       <c r="AE71" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="72" spans="2:31" x14ac:dyDescent="0.2">
+      <c r="AF71" s="3">
+        <v>0</v>
+      </c>
+      <c r="AG71" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="72" spans="2:33" x14ac:dyDescent="0.2">
       <c r="C72" s="1" t="s">
         <v>64</v>
       </c>
       <c r="D72" s="3">
+        <v>4382800</v>
+      </c>
+      <c r="E72" s="3">
+        <v>4382800</v>
+      </c>
+      <c r="F72" s="3">
         <v>4082500</v>
       </c>
-      <c r="E72" s="3">
+      <c r="G72" s="3">
         <v>4082500</v>
       </c>
-      <c r="F72" s="3">
+      <c r="H72" s="3">
         <v>3813300</v>
       </c>
-      <c r="G72" s="3">
+      <c r="I72" s="3">
         <v>3813300</v>
       </c>
-      <c r="H72" s="3">
+      <c r="J72" s="3">
         <v>3422500</v>
       </c>
-      <c r="I72" s="3">
+      <c r="K72" s="3">
         <v>3422500</v>
       </c>
-      <c r="J72" s="3">
+      <c r="L72" s="3">
         <v>3100000</v>
       </c>
-      <c r="K72" s="3">
+      <c r="M72" s="3">
         <v>3100000</v>
       </c>
-      <c r="L72" s="3">
+      <c r="N72" s="3">
         <v>2829800</v>
       </c>
-      <c r="M72" s="3">
+      <c r="O72" s="3">
         <v>2829800</v>
       </c>
-      <c r="N72" s="3">
+      <c r="P72" s="3">
         <v>2674100</v>
       </c>
-      <c r="O72" s="3">
+      <c r="Q72" s="3">
         <v>2674100</v>
       </c>
-      <c r="P72" s="3">
+      <c r="R72" s="3">
         <v>2328300</v>
       </c>
-      <c r="Q72" s="3">
+      <c r="S72" s="3">
         <v>3383900</v>
       </c>
-      <c r="R72" s="3">
+      <c r="T72" s="3">
         <v>3246900</v>
       </c>
-      <c r="S72" s="3">
+      <c r="U72" s="3">
         <v>3184000</v>
       </c>
-      <c r="T72" s="3">
+      <c r="V72" s="3">
         <v>3123900</v>
       </c>
-      <c r="U72" s="3">
+      <c r="W72" s="3">
         <v>3224400</v>
       </c>
-      <c r="V72" s="3">
+      <c r="X72" s="3">
         <v>3417600</v>
       </c>
-      <c r="W72" s="3">
+      <c r="Y72" s="3">
         <v>3466300</v>
       </c>
-      <c r="X72" s="3">
+      <c r="Z72" s="3">
         <v>3342900</v>
       </c>
-      <c r="Y72" s="3">
+      <c r="AA72" s="3">
         <v>3393100</v>
       </c>
-      <c r="Z72" s="3">
+      <c r="AB72" s="3">
         <v>3305400</v>
       </c>
-      <c r="AA72" s="3">
+      <c r="AC72" s="3">
         <v>3370700</v>
       </c>
-      <c r="AB72" s="3">
+      <c r="AD72" s="3">
         <v>1481800</v>
       </c>
-      <c r="AC72" s="3">
+      <c r="AE72" s="3">
         <v>1708200</v>
       </c>
-      <c r="AD72" s="3">
+      <c r="AF72" s="3">
         <v>1614100</v>
       </c>
-      <c r="AE72" s="3">
+      <c r="AG72" s="3">
         <v>1734300</v>
       </c>
     </row>
-    <row r="73" spans="2:31" x14ac:dyDescent="0.2">
+    <row r="73" spans="2:33" x14ac:dyDescent="0.2">
       <c r="C73" s="1" t="s">
         <v>65</v>
       </c>
@@ -6038,8 +6392,14 @@
       <c r="AE73" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="74" spans="2:31" x14ac:dyDescent="0.2">
+      <c r="AF73" s="3">
+        <v>0</v>
+      </c>
+      <c r="AG73" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="74" spans="2:33" x14ac:dyDescent="0.2">
       <c r="C74" s="1" t="s">
         <v>66</v>
       </c>
@@ -6127,8 +6487,14 @@
       <c r="AE74" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="75" spans="2:31" x14ac:dyDescent="0.2">
+      <c r="AF74" s="3">
+        <v>0</v>
+      </c>
+      <c r="AG74" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="75" spans="2:33" x14ac:dyDescent="0.2">
       <c r="C75" s="1" t="s">
         <v>67</v>
       </c>
@@ -6216,97 +6582,109 @@
       <c r="AE75" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="76" spans="2:31" x14ac:dyDescent="0.2">
+      <c r="AF75" s="3">
+        <v>0</v>
+      </c>
+      <c r="AG75" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="76" spans="2:33" x14ac:dyDescent="0.2">
       <c r="C76" s="1" t="s">
         <v>68</v>
       </c>
       <c r="D76" s="3">
+        <v>4443100</v>
+      </c>
+      <c r="E76" s="3">
+        <v>4443100</v>
+      </c>
+      <c r="F76" s="3">
         <v>4388800</v>
       </c>
-      <c r="E76" s="3">
+      <c r="G76" s="3">
         <v>4388800</v>
       </c>
-      <c r="F76" s="3">
+      <c r="H76" s="3">
         <v>4317200</v>
       </c>
-      <c r="G76" s="3">
+      <c r="I76" s="3">
         <v>4317200</v>
       </c>
-      <c r="H76" s="3">
+      <c r="J76" s="3">
         <v>3926200</v>
       </c>
-      <c r="I76" s="3">
+      <c r="K76" s="3">
         <v>3926200</v>
       </c>
-      <c r="J76" s="3">
+      <c r="L76" s="3">
         <v>3647600</v>
       </c>
-      <c r="K76" s="3">
+      <c r="M76" s="3">
         <v>3647600</v>
       </c>
-      <c r="L76" s="3">
+      <c r="N76" s="3">
         <v>3688000</v>
       </c>
-      <c r="M76" s="3">
+      <c r="O76" s="3">
         <v>3688000</v>
       </c>
-      <c r="N76" s="3">
+      <c r="P76" s="3">
         <v>3668500</v>
       </c>
-      <c r="O76" s="3">
+      <c r="Q76" s="3">
         <v>3668500</v>
       </c>
-      <c r="P76" s="3">
+      <c r="R76" s="3">
         <v>3296500</v>
       </c>
-      <c r="Q76" s="3">
+      <c r="S76" s="3">
         <v>3183600</v>
       </c>
-      <c r="R76" s="3">
+      <c r="T76" s="3">
         <v>3140000</v>
       </c>
-      <c r="S76" s="3">
+      <c r="U76" s="3">
         <v>2965200</v>
       </c>
-      <c r="T76" s="3">
+      <c r="V76" s="3">
         <v>2928700</v>
       </c>
-      <c r="U76" s="3">
+      <c r="W76" s="3">
         <v>2993300</v>
       </c>
-      <c r="V76" s="3">
+      <c r="X76" s="3">
         <v>3083600</v>
       </c>
-      <c r="W76" s="3">
+      <c r="Y76" s="3">
         <v>3105000</v>
       </c>
-      <c r="X76" s="3">
+      <c r="Z76" s="3">
         <v>3227100</v>
       </c>
-      <c r="Y76" s="3">
+      <c r="AA76" s="3">
         <v>3273800</v>
       </c>
-      <c r="Z76" s="3">
+      <c r="AB76" s="3">
         <v>3112000</v>
       </c>
-      <c r="AA76" s="3">
+      <c r="AC76" s="3">
         <v>3337000</v>
       </c>
-      <c r="AB76" s="3">
+      <c r="AD76" s="3">
         <v>3070200</v>
       </c>
-      <c r="AC76" s="3">
+      <c r="AE76" s="3">
         <v>3398900</v>
       </c>
-      <c r="AD76" s="3">
+      <c r="AF76" s="3">
         <v>3428400</v>
       </c>
-      <c r="AE76" s="3">
+      <c r="AG76" s="3">
         <v>3641100</v>
       </c>
     </row>
-    <row r="77" spans="2:31" x14ac:dyDescent="0.2">
+    <row r="77" spans="2:33" x14ac:dyDescent="0.2">
       <c r="C77" s="1" t="s">
         <v>69</v>
       </c>
@@ -6394,102 +6772,114 @@
       <c r="AE77" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="79" spans="2:31" x14ac:dyDescent="0.2">
+      <c r="AF77" s="3">
+        <v>0</v>
+      </c>
+      <c r="AG77" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="79" spans="2:33" x14ac:dyDescent="0.2">
       <c r="B79" s="1" t="s">
         <v>70</v>
       </c>
     </row>
-    <row r="80" spans="2:31" x14ac:dyDescent="0.2">
+    <row r="80" spans="2:33" x14ac:dyDescent="0.2">
       <c r="C80" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D80" s="2">
+        <v>46203</v>
+      </c>
+      <c r="E80" s="2">
+        <v>46112</v>
+      </c>
+      <c r="F80" s="2">
         <v>46022</v>
       </c>
-      <c r="E80" s="2">
+      <c r="G80" s="2">
         <v>45930</v>
       </c>
-      <c r="F80" s="2">
+      <c r="H80" s="2">
         <v>45838</v>
       </c>
-      <c r="G80" s="2">
+      <c r="I80" s="2">
         <v>45747</v>
       </c>
-      <c r="H80" s="2">
+      <c r="J80" s="2">
         <v>45657</v>
       </c>
-      <c r="I80" s="2">
+      <c r="K80" s="2">
         <v>45565</v>
       </c>
-      <c r="J80" s="2">
+      <c r="L80" s="2">
         <v>45473</v>
       </c>
-      <c r="K80" s="2">
+      <c r="M80" s="2">
         <v>45382</v>
       </c>
-      <c r="L80" s="2">
+      <c r="N80" s="2">
         <v>45291</v>
       </c>
-      <c r="M80" s="2">
+      <c r="O80" s="2">
         <v>45199</v>
       </c>
-      <c r="N80" s="2">
+      <c r="P80" s="2">
         <v>45107</v>
       </c>
-      <c r="O80" s="2">
+      <c r="Q80" s="2">
         <v>45016</v>
       </c>
-      <c r="P80" s="2">
+      <c r="R80" s="2">
         <v>44926</v>
       </c>
-      <c r="Q80" s="2">
+      <c r="S80" s="2">
         <v>44377</v>
       </c>
-      <c r="R80" s="2">
+      <c r="T80" s="2">
         <v>44196</v>
       </c>
-      <c r="S80" s="2">
+      <c r="U80" s="2">
         <v>44012</v>
       </c>
-      <c r="T80" s="2">
+      <c r="V80" s="2">
         <v>43830</v>
       </c>
-      <c r="U80" s="2">
+      <c r="W80" s="2">
         <v>43646</v>
       </c>
-      <c r="V80" s="2">
+      <c r="X80" s="2">
         <v>43465</v>
       </c>
-      <c r="W80" s="2">
+      <c r="Y80" s="2">
         <v>43281</v>
       </c>
-      <c r="X80" s="2">
+      <c r="Z80" s="2">
         <v>43100</v>
       </c>
-      <c r="Y80" s="2">
+      <c r="AA80" s="2">
         <v>42916</v>
       </c>
-      <c r="Z80" s="2">
+      <c r="AB80" s="2">
         <v>42735</v>
       </c>
-      <c r="AA80" s="2">
+      <c r="AC80" s="2">
         <v>42551</v>
       </c>
-      <c r="AB80" s="2">
+      <c r="AD80" s="2">
         <v>42369</v>
       </c>
-      <c r="AC80" s="2">
+      <c r="AE80" s="2">
         <v>42185</v>
       </c>
-      <c r="AD80" s="2">
+      <c r="AF80" s="2">
         <v>42004</v>
       </c>
-      <c r="AE80" s="2">
+      <c r="AG80" s="2">
         <v>41820</v>
       </c>
     </row>
-    <row r="81" spans="3:31" x14ac:dyDescent="0.2">
+    <row r="81" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C81" s="1" t="s">
         <v>28</v>
       </c>
@@ -6532,53 +6922,59 @@
       <c r="P81" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="Q81" s="3">
+      <c r="Q81" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="R81" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="S81" s="3">
         <v>181000</v>
       </c>
-      <c r="R81" s="3">
+      <c r="T81" s="3">
         <v>101000</v>
       </c>
-      <c r="S81" s="3">
+      <c r="U81" s="3">
         <v>100600</v>
       </c>
-      <c r="T81" s="3">
+      <c r="V81" s="3">
         <v>-105600</v>
       </c>
-      <c r="U81" s="3">
+      <c r="W81" s="3">
         <v>-148300</v>
       </c>
-      <c r="V81" s="3">
+      <c r="X81" s="3">
         <v>-2000</v>
       </c>
-      <c r="W81" s="3">
+      <c r="Y81" s="3">
         <v>133800</v>
       </c>
-      <c r="X81" s="3">
+      <c r="Z81" s="3">
         <v>-12200</v>
       </c>
-      <c r="Y81" s="3">
+      <c r="AA81" s="3">
         <v>133100</v>
       </c>
-      <c r="Z81" s="3">
+      <c r="AB81" s="3">
         <v>-24400</v>
       </c>
-      <c r="AA81" s="3">
+      <c r="AC81" s="3">
         <v>127600</v>
       </c>
-      <c r="AB81" s="3">
+      <c r="AD81" s="3">
         <v>-74500</v>
       </c>
-      <c r="AC81" s="3">
+      <c r="AE81" s="3">
         <v>157400</v>
       </c>
-      <c r="AD81" s="3">
+      <c r="AF81" s="3">
         <v>-105300</v>
       </c>
-      <c r="AE81" s="3">
+      <c r="AG81" s="3">
         <v>186300</v>
       </c>
     </row>
-    <row r="82" spans="3:31" x14ac:dyDescent="0.2">
+    <row r="82" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C82" s="1" t="s">
         <v>71</v>
       </c>
@@ -6610,97 +7006,105 @@
       <c r="AC82" s="3"/>
       <c r="AD82" s="3"/>
       <c r="AE82" s="3"/>
-    </row>
-    <row r="83" spans="3:31" x14ac:dyDescent="0.2">
+      <c r="AF82" s="3"/>
+      <c r="AG82" s="3"/>
+    </row>
+    <row r="83" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C83" s="1" t="s">
         <v>72</v>
       </c>
       <c r="D83" s="3">
+        <v>80300</v>
+      </c>
+      <c r="E83" s="3">
+        <v>80300</v>
+      </c>
+      <c r="F83" s="3">
         <v>83200</v>
       </c>
-      <c r="E83" s="3">
+      <c r="G83" s="3">
         <v>83200</v>
       </c>
-      <c r="F83" s="3">
+      <c r="H83" s="3">
         <v>75200</v>
       </c>
-      <c r="G83" s="3">
+      <c r="I83" s="3">
         <v>75200</v>
       </c>
-      <c r="H83" s="3">
+      <c r="J83" s="3">
         <v>85900</v>
       </c>
-      <c r="I83" s="3">
+      <c r="K83" s="3">
         <v>85900</v>
       </c>
-      <c r="J83" s="3">
+      <c r="L83" s="3">
         <v>84600</v>
       </c>
-      <c r="K83" s="3">
+      <c r="M83" s="3">
         <v>84600</v>
       </c>
-      <c r="L83" s="3">
+      <c r="N83" s="3">
         <v>82000</v>
       </c>
-      <c r="M83" s="3">
+      <c r="O83" s="3">
         <v>82000</v>
       </c>
-      <c r="N83" s="3">
+      <c r="P83" s="3">
         <v>82300</v>
       </c>
-      <c r="O83" s="3">
+      <c r="Q83" s="3">
         <v>82300</v>
       </c>
-      <c r="P83" s="3">
+      <c r="R83" s="3">
         <v>87100</v>
       </c>
-      <c r="Q83" s="3">
+      <c r="S83" s="3">
         <v>246300</v>
       </c>
-      <c r="R83" s="3">
+      <c r="T83" s="3">
         <v>294300</v>
       </c>
-      <c r="S83" s="3">
+      <c r="U83" s="3">
         <v>258600</v>
       </c>
-      <c r="T83" s="3">
+      <c r="V83" s="3">
         <v>275400</v>
       </c>
-      <c r="U83" s="3">
+      <c r="W83" s="3">
         <v>257800</v>
       </c>
-      <c r="V83" s="3">
+      <c r="X83" s="3">
         <v>251900</v>
       </c>
-      <c r="W83" s="3">
+      <c r="Y83" s="3">
         <v>209200</v>
       </c>
-      <c r="X83" s="3">
+      <c r="Z83" s="3">
         <v>243700</v>
       </c>
-      <c r="Y83" s="3">
+      <c r="AA83" s="3">
         <v>177500</v>
       </c>
-      <c r="Z83" s="3">
+      <c r="AB83" s="3">
         <v>183500</v>
       </c>
-      <c r="AA83" s="3">
+      <c r="AC83" s="3">
         <v>182300</v>
       </c>
-      <c r="AB83" s="3">
+      <c r="AD83" s="3">
         <v>189600</v>
       </c>
-      <c r="AC83" s="3">
+      <c r="AE83" s="3">
         <v>174500</v>
       </c>
-      <c r="AD83" s="3">
+      <c r="AF83" s="3">
         <v>171700</v>
       </c>
-      <c r="AE83" s="3">
+      <c r="AG83" s="3">
         <v>147800</v>
       </c>
     </row>
-    <row r="84" spans="3:31" x14ac:dyDescent="0.2">
+    <row r="84" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C84" s="1" t="s">
         <v>73</v>
       </c>
@@ -6788,8 +7192,14 @@
       <c r="AE84" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="85" spans="3:31" x14ac:dyDescent="0.2">
+      <c r="AF84" s="3">
+        <v>0</v>
+      </c>
+      <c r="AG84" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="85" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C85" s="1" t="s">
         <v>74</v>
       </c>
@@ -6877,8 +7287,14 @@
       <c r="AE85" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="86" spans="3:31" x14ac:dyDescent="0.2">
+      <c r="AF85" s="3">
+        <v>0</v>
+      </c>
+      <c r="AG85" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="86" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C86" s="1" t="s">
         <v>75</v>
       </c>
@@ -6966,8 +7382,14 @@
       <c r="AE86" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="87" spans="3:31" x14ac:dyDescent="0.2">
+      <c r="AF86" s="3">
+        <v>0</v>
+      </c>
+      <c r="AG86" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="87" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C87" s="1" t="s">
         <v>76</v>
       </c>
@@ -7055,8 +7477,14 @@
       <c r="AE87" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="88" spans="3:31" x14ac:dyDescent="0.2">
+      <c r="AF87" s="3">
+        <v>0</v>
+      </c>
+      <c r="AG87" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="88" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C88" s="1" t="s">
         <v>77</v>
       </c>
@@ -7144,97 +7572,109 @@
       <c r="AE88" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="89" spans="3:31" x14ac:dyDescent="0.2">
+      <c r="AF88" s="3">
+        <v>0</v>
+      </c>
+      <c r="AG88" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="89" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C89" s="1" t="s">
         <v>78</v>
       </c>
       <c r="D89" s="3">
+        <v>411200</v>
+      </c>
+      <c r="E89" s="3">
+        <v>411200</v>
+      </c>
+      <c r="F89" s="3">
         <v>455100</v>
       </c>
-      <c r="E89" s="3">
+      <c r="G89" s="3">
         <v>455100</v>
       </c>
-      <c r="F89" s="3">
+      <c r="H89" s="3">
         <v>419100</v>
       </c>
-      <c r="G89" s="3">
+      <c r="I89" s="3">
         <v>419100</v>
       </c>
-      <c r="H89" s="3">
+      <c r="J89" s="3">
         <v>533900</v>
       </c>
-      <c r="I89" s="3">
+      <c r="K89" s="3">
         <v>533900</v>
       </c>
-      <c r="J89" s="3">
+      <c r="L89" s="3">
         <v>339400</v>
       </c>
-      <c r="K89" s="3">
+      <c r="M89" s="3">
         <v>339400</v>
       </c>
-      <c r="L89" s="3">
+      <c r="N89" s="3">
         <v>600800</v>
       </c>
-      <c r="M89" s="3">
+      <c r="O89" s="3">
         <v>600800</v>
       </c>
-      <c r="N89" s="3">
+      <c r="P89" s="3">
         <v>264300</v>
       </c>
-      <c r="O89" s="3">
+      <c r="Q89" s="3">
         <v>264300</v>
       </c>
-      <c r="P89" s="3">
+      <c r="R89" s="3">
         <v>490900</v>
       </c>
-      <c r="Q89" s="3">
+      <c r="S89" s="3">
         <v>548800</v>
       </c>
-      <c r="R89" s="3">
+      <c r="T89" s="3">
         <v>660200</v>
       </c>
-      <c r="S89" s="3">
+      <c r="U89" s="3">
         <v>376400</v>
       </c>
-      <c r="T89" s="3">
+      <c r="V89" s="3">
         <v>874300</v>
       </c>
-      <c r="U89" s="3">
+      <c r="W89" s="3">
         <v>581200</v>
       </c>
-      <c r="V89" s="3">
+      <c r="X89" s="3">
         <v>335600</v>
       </c>
-      <c r="W89" s="3">
+      <c r="Y89" s="3">
         <v>398500</v>
       </c>
-      <c r="X89" s="3">
+      <c r="Z89" s="3">
         <v>480500</v>
       </c>
-      <c r="Y89" s="3">
+      <c r="AA89" s="3">
         <v>295600</v>
       </c>
-      <c r="Z89" s="3">
+      <c r="AB89" s="3">
         <v>656600</v>
       </c>
-      <c r="AA89" s="3">
+      <c r="AC89" s="3">
         <v>74800</v>
       </c>
-      <c r="AB89" s="3">
+      <c r="AD89" s="3">
         <v>254100</v>
       </c>
-      <c r="AC89" s="3">
+      <c r="AE89" s="3">
         <v>395900</v>
       </c>
-      <c r="AD89" s="3">
+      <c r="AF89" s="3">
         <v>478600</v>
       </c>
-      <c r="AE89" s="3">
+      <c r="AG89" s="3">
         <v>357200</v>
       </c>
     </row>
-    <row r="90" spans="3:31" x14ac:dyDescent="0.2">
+    <row r="90" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C90" s="1" t="s">
         <v>79</v>
       </c>
@@ -7266,97 +7706,105 @@
       <c r="AC90" s="3"/>
       <c r="AD90" s="3"/>
       <c r="AE90" s="3"/>
-    </row>
-    <row r="91" spans="3:31" x14ac:dyDescent="0.2">
+      <c r="AF90" s="3"/>
+      <c r="AG90" s="3"/>
+    </row>
+    <row r="91" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C91" s="1" t="s">
         <v>80</v>
       </c>
       <c r="D91" s="3">
+        <v>-140900</v>
+      </c>
+      <c r="E91" s="3">
+        <v>-140900</v>
+      </c>
+      <c r="F91" s="3">
         <v>-125800</v>
       </c>
-      <c r="E91" s="3">
+      <c r="G91" s="3">
         <v>-125800</v>
       </c>
-      <c r="F91" s="3">
+      <c r="H91" s="3">
         <v>-148000</v>
       </c>
-      <c r="G91" s="3">
+      <c r="I91" s="3">
         <v>-148000</v>
       </c>
-      <c r="H91" s="3">
+      <c r="J91" s="3">
         <v>-111000</v>
       </c>
-      <c r="I91" s="3">
+      <c r="K91" s="3">
         <v>-111000</v>
       </c>
-      <c r="J91" s="3">
+      <c r="L91" s="3">
         <v>-120100</v>
       </c>
-      <c r="K91" s="3">
+      <c r="M91" s="3">
         <v>-120100</v>
       </c>
-      <c r="L91" s="3">
+      <c r="N91" s="3">
         <v>-65200</v>
       </c>
-      <c r="M91" s="3">
+      <c r="O91" s="3">
         <v>-65200</v>
       </c>
-      <c r="N91" s="3">
+      <c r="P91" s="3">
         <v>-66300</v>
       </c>
-      <c r="O91" s="3">
+      <c r="Q91" s="3">
         <v>-66300</v>
       </c>
-      <c r="P91" s="3">
+      <c r="R91" s="3">
         <v>-102200</v>
       </c>
-      <c r="Q91" s="3">
+      <c r="S91" s="3">
         <v>-572900</v>
       </c>
-      <c r="R91" s="3">
+      <c r="T91" s="3">
         <v>-551400</v>
       </c>
-      <c r="S91" s="3">
+      <c r="U91" s="3">
         <v>-514200</v>
       </c>
-      <c r="T91" s="3">
+      <c r="V91" s="3">
         <v>-750300</v>
       </c>
-      <c r="U91" s="3">
+      <c r="W91" s="3">
         <v>-204900</v>
       </c>
-      <c r="V91" s="3">
+      <c r="X91" s="3">
         <v>-463600</v>
       </c>
-      <c r="W91" s="3">
+      <c r="Y91" s="3">
         <v>-202100</v>
       </c>
-      <c r="X91" s="3">
+      <c r="Z91" s="3">
         <v>-294500</v>
       </c>
-      <c r="Y91" s="3">
+      <c r="AA91" s="3">
         <v>-319600</v>
       </c>
-      <c r="Z91" s="3">
+      <c r="AB91" s="3">
         <v>-129700</v>
       </c>
-      <c r="AA91" s="3">
+      <c r="AC91" s="3">
         <v>-189800</v>
       </c>
-      <c r="AB91" s="3">
+      <c r="AD91" s="3">
         <v>-39900</v>
       </c>
-      <c r="AC91" s="3">
+      <c r="AE91" s="3">
         <v>-37300</v>
       </c>
-      <c r="AD91" s="3">
+      <c r="AF91" s="3">
         <v>-309600</v>
       </c>
-      <c r="AE91" s="3">
+      <c r="AG91" s="3">
         <v>-326800</v>
       </c>
     </row>
-    <row r="92" spans="3:31" x14ac:dyDescent="0.2">
+    <row r="92" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C92" s="1" t="s">
         <v>81</v>
       </c>
@@ -7444,8 +7892,14 @@
       <c r="AE92" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="93" spans="3:31" x14ac:dyDescent="0.2">
+      <c r="AF92" s="3">
+        <v>0</v>
+      </c>
+      <c r="AG92" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="93" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C93" s="1" t="s">
         <v>82</v>
       </c>
@@ -7533,97 +7987,109 @@
       <c r="AE93" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="94" spans="3:31" x14ac:dyDescent="0.2">
+      <c r="AF93" s="3">
+        <v>0</v>
+      </c>
+      <c r="AG93" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="94" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C94" s="1" t="s">
         <v>83</v>
       </c>
       <c r="D94" s="3">
+        <v>-252200</v>
+      </c>
+      <c r="E94" s="3">
+        <v>-252200</v>
+      </c>
+      <c r="F94" s="3">
         <v>-364600</v>
       </c>
-      <c r="E94" s="3">
+      <c r="G94" s="3">
         <v>-364600</v>
       </c>
-      <c r="F94" s="3">
+      <c r="H94" s="3">
         <v>-184000</v>
       </c>
-      <c r="G94" s="3">
+      <c r="I94" s="3">
         <v>-184000</v>
       </c>
-      <c r="H94" s="3">
+      <c r="J94" s="3">
         <v>-618400</v>
       </c>
-      <c r="I94" s="3">
+      <c r="K94" s="3">
         <v>-618400</v>
       </c>
-      <c r="J94" s="3">
+      <c r="L94" s="3">
         <v>-198100</v>
       </c>
-      <c r="K94" s="3">
+      <c r="M94" s="3">
         <v>-198100</v>
       </c>
-      <c r="L94" s="3">
+      <c r="N94" s="3">
         <v>-538400</v>
       </c>
-      <c r="M94" s="3">
+      <c r="O94" s="3">
         <v>-538400</v>
       </c>
-      <c r="N94" s="3">
+      <c r="P94" s="3">
         <v>-203700</v>
       </c>
-      <c r="O94" s="3">
+      <c r="Q94" s="3">
         <v>-203700</v>
       </c>
-      <c r="P94" s="3">
+      <c r="R94" s="3">
         <v>-513300</v>
       </c>
-      <c r="Q94" s="3">
+      <c r="S94" s="3">
         <v>-449100</v>
       </c>
-      <c r="R94" s="3">
+      <c r="T94" s="3">
         <v>-2319700</v>
       </c>
-      <c r="S94" s="3">
+      <c r="U94" s="3">
         <v>-628200</v>
       </c>
-      <c r="T94" s="3">
+      <c r="V94" s="3">
         <v>128800</v>
       </c>
-      <c r="U94" s="3">
+      <c r="W94" s="3">
         <v>-462500</v>
       </c>
-      <c r="V94" s="3">
+      <c r="X94" s="3">
         <v>-1003100</v>
       </c>
-      <c r="W94" s="3">
+      <c r="Y94" s="3">
         <v>-325500</v>
       </c>
-      <c r="X94" s="3">
+      <c r="Z94" s="3">
         <v>-523800</v>
       </c>
-      <c r="Y94" s="3">
+      <c r="AA94" s="3">
         <v>-164000</v>
       </c>
-      <c r="Z94" s="3">
+      <c r="AB94" s="3">
         <v>31000</v>
       </c>
-      <c r="AA94" s="3">
+      <c r="AC94" s="3">
         <v>-819500</v>
       </c>
-      <c r="AB94" s="3">
+      <c r="AD94" s="3">
         <v>-383500</v>
       </c>
-      <c r="AC94" s="3">
+      <c r="AE94" s="3">
         <v>-1494900</v>
       </c>
-      <c r="AD94" s="3">
+      <c r="AF94" s="3">
         <v>-497800</v>
       </c>
-      <c r="AE94" s="3">
+      <c r="AG94" s="3">
         <v>-641100</v>
       </c>
     </row>
-    <row r="95" spans="3:31" x14ac:dyDescent="0.2">
+    <row r="95" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C95" s="1" t="s">
         <v>84</v>
       </c>
@@ -7655,97 +8121,105 @@
       <c r="AC95" s="3"/>
       <c r="AD95" s="3"/>
       <c r="AE95" s="3"/>
-    </row>
-    <row r="96" spans="3:31" x14ac:dyDescent="0.2">
+      <c r="AF95" s="3"/>
+      <c r="AG95" s="3"/>
+    </row>
+    <row r="96" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C96" s="1" t="s">
         <v>85</v>
       </c>
       <c r="D96" s="3">
+        <v>39600</v>
+      </c>
+      <c r="E96" s="3">
+        <v>39600</v>
+      </c>
+      <c r="F96" s="3">
         <v>72300</v>
       </c>
-      <c r="E96" s="3">
+      <c r="G96" s="3">
         <v>72300</v>
       </c>
-      <c r="F96" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="G96" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="H96" s="3">
+      <c r="H96" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="I96" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="J96" s="3">
         <v>66600</v>
       </c>
-      <c r="I96" s="3">
+      <c r="K96" s="3">
         <v>66600</v>
       </c>
-      <c r="J96" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="K96" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="L96" s="3">
+      <c r="L96" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="M96" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="N96" s="3">
         <v>59500</v>
       </c>
-      <c r="M96" s="3">
+      <c r="O96" s="3">
         <v>59500</v>
       </c>
-      <c r="N96" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="O96" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="P96" s="3">
+      <c r="P96" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="Q96" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="R96" s="3">
         <v>55600</v>
       </c>
-      <c r="Q96" s="3">
-        <v>0</v>
-      </c>
-      <c r="R96" s="3">
-        <v>0</v>
-      </c>
       <c r="S96" s="3">
         <v>0</v>
       </c>
       <c r="T96" s="3">
+        <v>0</v>
+      </c>
+      <c r="U96" s="3">
+        <v>0</v>
+      </c>
+      <c r="V96" s="3">
         <v>-66600</v>
       </c>
-      <c r="U96" s="3">
-        <v>0</v>
-      </c>
-      <c r="V96" s="3">
+      <c r="W96" s="3">
+        <v>0</v>
+      </c>
+      <c r="X96" s="3">
         <v>-44200</v>
       </c>
-      <c r="W96" s="3">
+      <c r="Y96" s="3">
         <v>-30400</v>
       </c>
-      <c r="X96" s="3">
+      <c r="Z96" s="3">
         <v>-44300</v>
       </c>
-      <c r="Y96" s="3">
+      <c r="AA96" s="3">
         <v>-30500</v>
-      </c>
-      <c r="Z96" s="3">
-        <v>-44000</v>
-      </c>
-      <c r="AA96" s="3">
-        <v>-30200</v>
       </c>
       <c r="AB96" s="3">
         <v>-44000</v>
       </c>
       <c r="AC96" s="3">
+        <v>-30200</v>
+      </c>
+      <c r="AD96" s="3">
+        <v>-44000</v>
+      </c>
+      <c r="AE96" s="3">
         <v>-71500</v>
       </c>
-      <c r="AD96" s="3">
+      <c r="AF96" s="3">
         <v>-44200</v>
       </c>
-      <c r="AE96" s="3">
+      <c r="AG96" s="3">
         <v>-71700</v>
       </c>
     </row>
-    <row r="97" spans="3:31" x14ac:dyDescent="0.2">
+    <row r="97" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C97" s="1" t="s">
         <v>86</v>
       </c>
@@ -7833,8 +8307,14 @@
       <c r="AE97" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="98" spans="3:31" x14ac:dyDescent="0.2">
+      <c r="AF97" s="3">
+        <v>0</v>
+      </c>
+      <c r="AG97" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="98" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C98" s="1" t="s">
         <v>87</v>
       </c>
@@ -7922,8 +8402,14 @@
       <c r="AE98" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="99" spans="3:31" x14ac:dyDescent="0.2">
+      <c r="AF98" s="3">
+        <v>0</v>
+      </c>
+      <c r="AG98" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="99" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C99" s="1" t="s">
         <v>88</v>
       </c>
@@ -8011,271 +8497,295 @@
       <c r="AE99" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="100" spans="3:31" x14ac:dyDescent="0.2">
+      <c r="AF99" s="3">
+        <v>0</v>
+      </c>
+      <c r="AG99" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="100" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C100" s="1" t="s">
         <v>89</v>
       </c>
       <c r="D100" s="3">
+        <v>46900</v>
+      </c>
+      <c r="E100" s="3">
+        <v>46900</v>
+      </c>
+      <c r="F100" s="3">
         <v>254000</v>
       </c>
-      <c r="E100" s="3">
+      <c r="G100" s="3">
         <v>254000</v>
       </c>
-      <c r="F100" s="3">
+      <c r="H100" s="3">
         <v>-116500</v>
       </c>
-      <c r="G100" s="3">
+      <c r="I100" s="3">
         <v>-116500</v>
       </c>
-      <c r="H100" s="3">
+      <c r="J100" s="3">
         <v>216100</v>
       </c>
-      <c r="I100" s="3">
+      <c r="K100" s="3">
         <v>216100</v>
       </c>
-      <c r="J100" s="3">
+      <c r="L100" s="3">
         <v>17400</v>
       </c>
-      <c r="K100" s="3">
+      <c r="M100" s="3">
         <v>17400</v>
       </c>
-      <c r="L100" s="3">
+      <c r="N100" s="3">
         <v>6800</v>
       </c>
-      <c r="M100" s="3">
+      <c r="O100" s="3">
         <v>6800</v>
       </c>
-      <c r="N100" s="3">
+      <c r="P100" s="3">
         <v>37200</v>
       </c>
-      <c r="O100" s="3">
+      <c r="Q100" s="3">
         <v>37200</v>
       </c>
-      <c r="P100" s="3">
+      <c r="R100" s="3">
         <v>-27300</v>
       </c>
-      <c r="Q100" s="3">
+      <c r="S100" s="3">
         <v>66800</v>
       </c>
-      <c r="R100" s="3">
+      <c r="T100" s="3">
         <v>1205300</v>
       </c>
-      <c r="S100" s="3">
+      <c r="U100" s="3">
         <v>360100</v>
       </c>
-      <c r="T100" s="3">
+      <c r="V100" s="3">
         <v>-10100</v>
       </c>
-      <c r="U100" s="3">
+      <c r="W100" s="3">
         <v>-124100</v>
       </c>
-      <c r="V100" s="3">
+      <c r="X100" s="3">
         <v>434600</v>
       </c>
-      <c r="W100" s="3">
+      <c r="Y100" s="3">
         <v>-118600</v>
       </c>
-      <c r="X100" s="3">
+      <c r="Z100" s="3">
         <v>197800</v>
       </c>
-      <c r="Y100" s="3">
+      <c r="AA100" s="3">
         <v>94000</v>
       </c>
-      <c r="Z100" s="3">
+      <c r="AB100" s="3">
         <v>-461700</v>
       </c>
-      <c r="AA100" s="3">
+      <c r="AC100" s="3">
         <v>696200</v>
       </c>
-      <c r="AB100" s="3">
+      <c r="AD100" s="3">
         <v>57600</v>
       </c>
-      <c r="AC100" s="3">
+      <c r="AE100" s="3">
         <v>640000</v>
       </c>
-      <c r="AD100" s="3">
+      <c r="AF100" s="3">
         <v>124900</v>
       </c>
-      <c r="AE100" s="3">
+      <c r="AG100" s="3">
         <v>284900</v>
       </c>
     </row>
-    <row r="101" spans="3:31" x14ac:dyDescent="0.2">
+    <row r="101" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C101" s="1" t="s">
         <v>90</v>
       </c>
       <c r="D101" s="3">
+        <v>16800</v>
+      </c>
+      <c r="E101" s="3">
+        <v>16800</v>
+      </c>
+      <c r="F101" s="3">
         <v>-1100</v>
       </c>
-      <c r="E101" s="3">
+      <c r="G101" s="3">
         <v>-1100</v>
       </c>
-      <c r="F101" s="3">
+      <c r="H101" s="3">
         <v>-52800</v>
       </c>
-      <c r="G101" s="3">
+      <c r="I101" s="3">
         <v>-52800</v>
       </c>
-      <c r="H101" s="3">
+      <c r="J101" s="3">
         <v>-12100</v>
       </c>
-      <c r="I101" s="3">
+      <c r="K101" s="3">
         <v>-12100</v>
       </c>
-      <c r="J101" s="3">
+      <c r="L101" s="3">
         <v>23300</v>
       </c>
-      <c r="K101" s="3">
+      <c r="M101" s="3">
         <v>23300</v>
       </c>
-      <c r="L101" s="3">
+      <c r="N101" s="3">
         <v>-8500</v>
       </c>
-      <c r="M101" s="3">
+      <c r="O101" s="3">
         <v>-8500</v>
       </c>
-      <c r="N101" s="3">
+      <c r="P101" s="3">
         <v>-66600</v>
       </c>
-      <c r="O101" s="3">
+      <c r="Q101" s="3">
         <v>-66600</v>
       </c>
-      <c r="P101" s="3">
+      <c r="R101" s="3">
         <v>-8100</v>
       </c>
-      <c r="Q101" s="3">
+      <c r="S101" s="3">
         <v>-51000</v>
       </c>
-      <c r="R101" s="3">
+      <c r="T101" s="3">
         <v>52300</v>
       </c>
-      <c r="S101" s="3">
+      <c r="U101" s="3">
         <v>6000</v>
       </c>
-      <c r="T101" s="3">
+      <c r="V101" s="3">
         <v>17600</v>
       </c>
-      <c r="U101" s="3">
+      <c r="W101" s="3">
         <v>32200</v>
       </c>
-      <c r="V101" s="3">
+      <c r="X101" s="3">
         <v>10500</v>
       </c>
-      <c r="W101" s="3">
+      <c r="Y101" s="3">
         <v>-105900</v>
       </c>
-      <c r="X101" s="3">
+      <c r="Z101" s="3">
         <v>-4400</v>
       </c>
-      <c r="Y101" s="3">
+      <c r="AA101" s="3">
         <v>400</v>
       </c>
-      <c r="Z101" s="3">
+      <c r="AB101" s="3">
         <v>-47400</v>
       </c>
-      <c r="AA101" s="3">
+      <c r="AC101" s="3">
         <v>31200</v>
       </c>
-      <c r="AB101" s="3">
+      <c r="AD101" s="3">
         <v>-8600</v>
       </c>
-      <c r="AC101" s="3">
+      <c r="AE101" s="3">
         <v>-96900</v>
       </c>
-      <c r="AD101" s="3">
+      <c r="AF101" s="3">
         <v>-36200</v>
       </c>
-      <c r="AE101" s="3">
+      <c r="AG101" s="3">
         <v>13000</v>
       </c>
     </row>
-    <row r="102" spans="3:31" x14ac:dyDescent="0.2">
+    <row r="102" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C102" s="1" t="s">
         <v>91</v>
       </c>
       <c r="D102" s="3">
+        <v>117100</v>
+      </c>
+      <c r="E102" s="3">
+        <v>117100</v>
+      </c>
+      <c r="F102" s="3">
         <v>295800</v>
       </c>
-      <c r="E102" s="3">
+      <c r="G102" s="3">
         <v>295800</v>
       </c>
-      <c r="F102" s="3">
+      <c r="H102" s="3">
         <v>135500</v>
       </c>
-      <c r="G102" s="3">
+      <c r="I102" s="3">
         <v>135500</v>
       </c>
-      <c r="H102" s="3">
+      <c r="J102" s="3">
         <v>130500</v>
       </c>
-      <c r="I102" s="3">
+      <c r="K102" s="3">
         <v>130500</v>
       </c>
-      <c r="J102" s="3">
+      <c r="L102" s="3">
         <v>105900</v>
       </c>
-      <c r="K102" s="3">
+      <c r="M102" s="3">
         <v>105900</v>
       </c>
-      <c r="L102" s="3">
+      <c r="N102" s="3">
         <v>57200</v>
       </c>
-      <c r="M102" s="3">
+      <c r="O102" s="3">
         <v>57200</v>
       </c>
-      <c r="N102" s="3">
+      <c r="P102" s="3">
         <v>121100</v>
       </c>
-      <c r="O102" s="3">
+      <c r="Q102" s="3">
         <v>121100</v>
       </c>
-      <c r="P102" s="3">
+      <c r="R102" s="3">
         <v>-58100</v>
       </c>
-      <c r="Q102" s="3">
+      <c r="S102" s="3">
         <v>115500</v>
       </c>
-      <c r="R102" s="3">
+      <c r="T102" s="3">
         <v>-401900</v>
       </c>
-      <c r="S102" s="3">
+      <c r="U102" s="3">
         <v>114300</v>
       </c>
-      <c r="T102" s="3">
+      <c r="V102" s="3">
         <v>1010600</v>
       </c>
-      <c r="U102" s="3">
+      <c r="W102" s="3">
         <v>26800</v>
       </c>
-      <c r="V102" s="3">
+      <c r="X102" s="3">
         <v>-222400</v>
       </c>
-      <c r="W102" s="3">
+      <c r="Y102" s="3">
         <v>-151500</v>
       </c>
-      <c r="X102" s="3">
+      <c r="Z102" s="3">
         <v>150100</v>
       </c>
-      <c r="Y102" s="3">
+      <c r="AA102" s="3">
         <v>226000</v>
       </c>
-      <c r="Z102" s="3">
+      <c r="AB102" s="3">
         <v>178500</v>
       </c>
-      <c r="AA102" s="3">
+      <c r="AC102" s="3">
         <v>-17300</v>
       </c>
-      <c r="AB102" s="3">
+      <c r="AD102" s="3">
         <v>-80400</v>
       </c>
-      <c r="AC102" s="3">
+      <c r="AE102" s="3">
         <v>-555900</v>
       </c>
-      <c r="AD102" s="3">
+      <c r="AF102" s="3">
         <v>69500</v>
       </c>
-      <c r="AE102" s="3">
+      <c r="AG102" s="3">
         <v>14000</v>
       </c>
     </row>
